--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -385,6 +385,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -752,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN88"/>
+  <dimension ref="A1:AN93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -12571,7 +12574,7 @@
     <row r="71">
       <c r="A71" s="51" t="inlineStr">
         <is>
-          <t>Aarón Eduardo Espinosa Espinosa</t>
+          <t>Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="B71" s="52" t="inlineStr">
@@ -12581,7 +12584,7 @@
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>58660078000</t>
+          <t>59326410200</t>
         </is>
       </c>
       <c r="D71" s="55" t="inlineStr">
@@ -12634,19 +12637,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N71" s="58" t="n">
-        <v>1</v>
+      <c r="N71" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P71" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="57" t="n">
-        <v>1</v>
+      <c r="P71" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q71" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R71" s="55" t="inlineStr">
         <is>
@@ -12678,20 +12687,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X71" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X71" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="Y71" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z71" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z71" s="54" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="55" t="inlineStr">
         <is>
@@ -12708,15 +12713,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD71" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE71" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD71" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE71" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="AF71" s="55" t="inlineStr">
         <is>
@@ -12757,13 +12758,13 @@
         <v>1</v>
       </c>
       <c r="AN71" s="43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>Daniel Toro Gonzalez</t>
+          <t>Gabriel Roman Melendez</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
@@ -12773,11 +12774,13 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>56380539800</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>1</v>
+          <t>56006978600</t>
+        </is>
+      </c>
+      <c r="D72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
         <is>
@@ -12799,11 +12802,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I72" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="45" t="n">
-        <v>1</v>
+      <c r="I72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K72" s="36" t="inlineStr">
         <is>
@@ -12820,25 +12827,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N72" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N72" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O72" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P72" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P72" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="47" t="n">
+        <v>1</v>
       </c>
       <c r="R72" s="37" t="inlineStr">
         <is>
@@ -12953,33 +12954,220 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
-        </is>
+      <c r="A73" s="51" t="inlineStr">
+        <is>
+          <t>Aarón Eduardo Espinosa Espinosa</t>
+        </is>
+      </c>
+      <c r="B73" s="52" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C73" s="52" t="inlineStr">
+        <is>
+          <t>58660078000</t>
+        </is>
+      </c>
+      <c r="D73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL73" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM73" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN73" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Daniel Toro Gonzalez</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>57191333650</t>
+          <t>56380539800</t>
         </is>
       </c>
       <c r="D74" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="8" t="n">
-        <v>2</v>
+      <c r="E74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F74" s="35" t="inlineStr">
         <is>
@@ -12997,41 +13185,55 @@
         </is>
       </c>
       <c r="I74" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J74" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="K74" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L74" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M74" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="15" t="n">
-        <v>1</v>
+      <c r="M74" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O74" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P74" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q74" s="47" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>2</v>
+      <c r="P74" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="T74" s="37" t="inlineStr">
         <is>
@@ -13048,17 +13250,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W74" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="X74" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y74" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z74" s="23" t="n">
-        <v>3</v>
+      <c r="W74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA74" s="38" t="inlineStr">
         <is>
@@ -13075,20 +13285,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD74" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE74" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF74" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG74" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH74" s="29" t="n">
-        <v>2</v>
+      <c r="AD74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI74" s="41" t="inlineStr">
         <is>
@@ -13100,33 +13320,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK74" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL74" s="50" t="n">
-        <v>7</v>
+      <c r="AK74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM74" s="42" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AN74" s="43" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="51" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="B75" s="52" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>57193012270</t>
+          <t>59326202000</t>
         </is>
       </c>
       <c r="D75" s="55" t="inlineStr">
@@ -13134,11 +13358,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E75" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="61" t="n">
-        <v>1</v>
+      <c r="E75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G75" s="55" t="inlineStr">
         <is>
@@ -13150,64 +13378,88 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I75" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K75" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="L75" s="54" t="n">
-        <v>2</v>
+      <c r="I75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M75" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N75" s="58" t="n">
-        <v>1</v>
+      <c r="N75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O75" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P75" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q75" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" s="53" t="n">
+      <c r="P75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X75" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="S75" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U75" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V75" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W75" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="X75" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y75" s="53" t="n">
-        <v>1</v>
+      <c r="Y75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z75" s="55" t="inlineStr">
         <is>
@@ -13229,20 +13481,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD75" s="56" t="n">
-        <v>1</v>
+      <c r="AD75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE75" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF75" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="AG75" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH75" s="61" t="n">
-        <v>2</v>
+      <c r="AF75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI75" s="55" t="inlineStr">
         <is>
@@ -13254,37 +13514,43 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK75" s="56" t="n">
+      <c r="AK75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL75" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM75" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="43" t="n">
         <v>6</v>
-      </c>
-      <c r="AL75" s="57" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM75" s="42" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN75" s="43" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Juan Camilo Medellin Rojas</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>57156565000</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>1</v>
+          <t>60150905000</t>
+        </is>
+      </c>
+      <c r="D76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
@@ -13306,22 +13572,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I76" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>3</v>
+      <c r="I76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L76" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M76" s="14" t="n">
-        <v>1</v>
+      <c r="M76" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N76" s="36" t="inlineStr">
         <is>
@@ -13333,14 +13607,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P76" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q76" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="R76" s="17" t="n">
-        <v>1</v>
+      <c r="P76" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R76" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S76" s="37" t="inlineStr">
         <is>
@@ -13362,14 +13642,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W76" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y76" s="22" t="n">
-        <v>1</v>
+      <c r="W76" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X76" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y76" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z76" s="38" t="inlineStr">
         <is>
@@ -13391,14 +13677,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD76" s="39" t="n">
-        <v>1</v>
+      <c r="AD76" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE76" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF76" s="27" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AF76" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG76" s="41" t="inlineStr">
         <is>
@@ -13420,37 +13710,43 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK76" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL76" s="50" t="n">
-        <v>1</v>
+      <c r="AK76" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL76" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM76" s="42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AN76" s="43" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="51" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo</t>
+          <t>Martha Patricia Castro Porto</t>
         </is>
       </c>
       <c r="B77" s="52" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>57202285682</t>
-        </is>
-      </c>
-      <c r="D77" s="53" t="n">
-        <v>1</v>
+          <t>58928816700</t>
+        </is>
+      </c>
+      <c r="D77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E77" s="55" t="inlineStr">
         <is>
@@ -13472,17 +13768,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I77" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="K77" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="54" t="n">
-        <v>1</v>
+      <c r="I77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M77" s="55" t="inlineStr">
         <is>
@@ -13499,284 +13803,135 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P77" s="56" t="n">
+      <c r="P77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q77" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X77" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL77" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM77" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="43" t="n">
         <v>2</v>
-      </c>
-      <c r="Q77" s="57" t="n">
-        <v>12</v>
-      </c>
-      <c r="R77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X77" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y77" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z77" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD77" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE77" s="57" t="n">
-        <v>31</v>
-      </c>
-      <c r="AF77" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ77" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK77" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL77" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM77" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN77" s="43" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="33" t="inlineStr">
-        <is>
-          <t>Juan Carlos Martinez Santos</t>
-        </is>
-      </c>
-      <c r="B78" s="34" t="inlineStr">
-        <is>
-          <t>Escuela de Transformación Digital</t>
-        </is>
-      </c>
-      <c r="C78" s="34" t="inlineStr">
-        <is>
-          <t>26325154200</t>
-        </is>
-      </c>
-      <c r="D78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J78" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q78" s="47" t="n">
-        <v>14</v>
-      </c>
-      <c r="R78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X78" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y78" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z78" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB78" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC78" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD78" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE78" s="40" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF78" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG78" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH78" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI78" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ78" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK78" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL78" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM78" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN78" s="43" t="n">
-        <v>71</v>
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="51" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B79" s="52" t="inlineStr">
@@ -13786,16 +13941,14 @@
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>57216868622</t>
-        </is>
-      </c>
-      <c r="D79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57191333650</t>
+        </is>
+      </c>
+      <c r="D79" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="E79" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="55" t="inlineStr">
         <is>
@@ -13813,50 +13966,42 @@
         </is>
       </c>
       <c r="I79" s="56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q79" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="T79" s="55" t="inlineStr">
         <is>
           <t>—</t>
@@ -13872,20 +14017,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W79" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="X79" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y79" s="53" t="n">
+        <v>6</v>
       </c>
       <c r="Z79" s="54" t="n">
         <v>3</v>
@@ -13906,25 +14045,19 @@
         </is>
       </c>
       <c r="AD79" s="56" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE79" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="AF79" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG79" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH79" s="61" t="n">
+        <v>2</v>
       </c>
       <c r="AI79" s="55" t="inlineStr">
         <is>
@@ -13936,27 +14069,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL79" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK79" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL79" s="57" t="n">
+        <v>7</v>
       </c>
       <c r="AM79" s="42" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AN79" s="43" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -13966,7 +14095,7 @@
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>57193012270</t>
         </is>
       </c>
       <c r="D80" s="35" t="inlineStr">
@@ -13974,15 +14103,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G80" s="35" t="inlineStr">
         <is>
@@ -13994,144 +14119,118 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I80" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="M80" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N80" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O80" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P80" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q80" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="T80" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U80" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V80" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X80" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W80" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="X80" s="49" t="n">
+        <v>5</v>
       </c>
       <c r="Y80" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD80" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE80" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="Z80" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA80" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB80" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC80" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD80" s="39" t="n">
+      <c r="AF80" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="AE80" s="40" t="n">
+      <c r="AG80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH80" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI80" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ80" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK80" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL80" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM80" s="42" t="n">
         <v>19</v>
-      </c>
-      <c r="AF80" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG80" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH80" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI80" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ80" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK80" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL80" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM80" s="42" t="n">
-        <v>4</v>
       </c>
       <c r="AN80" s="43" t="n">
         <v>20</v>
@@ -14140,7 +14239,7 @@
     <row r="81">
       <c r="A81" s="51" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B81" s="52" t="inlineStr">
@@ -14150,13 +14249,11 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>57206773929</t>
-        </is>
-      </c>
-      <c r="D81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57156565000</t>
+        </is>
+      </c>
+      <c r="D81" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="E81" s="55" t="inlineStr">
         <is>
@@ -14178,47 +14275,41 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I81" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="K81" s="53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M81" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="N81" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O81" s="62" t="n">
-        <v>1</v>
+      <c r="O81" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P81" s="56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q81" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R81" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="S81" s="55" t="inlineStr">
         <is>
@@ -14230,8 +14321,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U81" s="58" t="n">
-        <v>1</v>
+      <c r="U81" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V81" s="55" t="inlineStr">
         <is>
@@ -14242,15 +14335,15 @@
         <v>1</v>
       </c>
       <c r="X81" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z81" s="54" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="Y81" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA81" s="55" t="inlineStr">
         <is>
@@ -14271,12 +14364,10 @@
         <v>1</v>
       </c>
       <c r="AE81" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="AF81" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AG81" s="55" t="inlineStr">
         <is>
@@ -14298,27 +14389,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL81" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK81" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL81" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="AM81" s="42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN81" s="43" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes</t>
+          <t>Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
@@ -14328,16 +14415,16 @@
       </c>
       <c r="C82" s="34" t="inlineStr">
         <is>
-          <t>57221229836</t>
-        </is>
-      </c>
-      <c r="D82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>1</v>
+          <t>57202285682</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F82" s="35" t="inlineStr">
         <is>
@@ -14358,17 +14445,13 @@
         <v>1</v>
       </c>
       <c r="J82" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="M82" s="36" t="inlineStr">
         <is>
@@ -14385,15 +14468,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P82" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q82" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P82" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="47" t="n">
+        <v>12</v>
       </c>
       <c r="R82" s="37" t="inlineStr">
         <is>
@@ -14405,8 +14484,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T82" s="19" t="n">
-        <v>1</v>
+      <c r="T82" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U82" s="37" t="inlineStr">
         <is>
@@ -14418,16 +14499,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W82" s="48" t="n">
-        <v>1</v>
+      <c r="W82" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X82" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="Y82" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="Z82" s="23" t="n">
         <v>1</v>
@@ -14448,15 +14529,13 @@
         </is>
       </c>
       <c r="AD82" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE82" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF82" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="AF82" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG82" s="41" t="inlineStr">
         <is>
@@ -14478,27 +14557,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK82" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL82" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK82" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL82" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AM82" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN82" s="43" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="51" t="inlineStr">
         <is>
-          <t>Misorly del Carmen Soto Acevedo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="B83" s="52" t="inlineStr">
@@ -14508,7 +14583,7 @@
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>58523088300</t>
+          <t>26325154200</t>
         </is>
       </c>
       <c r="D83" s="55" t="inlineStr">
@@ -14541,23 +14616,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="61" t="n">
-        <v>1</v>
+      <c r="J83" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K83" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N83" s="55" t="inlineStr">
         <is>
@@ -14570,10 +14641,10 @@
         </is>
       </c>
       <c r="P83" s="56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="57" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R83" s="55" t="inlineStr">
         <is>
@@ -14605,20 +14676,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X83" s="57" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y83" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="54" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="55" t="inlineStr">
         <is>
@@ -14635,20 +14700,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD83" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE83" s="57" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF83" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AG83" s="55" t="inlineStr">
         <is>
@@ -14670,27 +14729,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL83" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK83" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL83" s="57" t="n">
+        <v>4</v>
       </c>
       <c r="AM83" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN83" s="43" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -14700,7 +14755,7 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>57220927199</t>
+          <t>57216868622</t>
         </is>
       </c>
       <c r="D84" s="35" t="inlineStr">
@@ -14708,10 +14763,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E84" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F84" s="35" t="inlineStr">
         <is>
@@ -14728,13 +14781,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I84" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I84" s="44" t="n">
+        <v>1</v>
       </c>
       <c r="J84" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="36" t="inlineStr">
         <is>
@@ -14746,10 +14797,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M84" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M84" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="N84" s="36" t="inlineStr">
         <is>
@@ -14761,13 +14810,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P84" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P84" s="46" t="n">
+        <v>1</v>
       </c>
       <c r="Q84" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R84" s="37" t="inlineStr">
         <is>
@@ -14799,18 +14846,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X84" s="49" t="n">
-        <v>2</v>
+      <c r="X84" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y84" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z84" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="AA84" s="38" t="inlineStr">
         <is>
@@ -14827,13 +14874,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD84" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="AE84" s="40" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AF84" s="41" t="inlineStr">
         <is>
@@ -14865,20 +14910,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL84" s="50" t="n">
-        <v>2</v>
+      <c r="AL84" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM84" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN84" s="43" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="51" t="inlineStr">
         <is>
-          <t>Julio Antonio Gomez Mora</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B85" s="52" t="inlineStr">
@@ -14888,7 +14935,7 @@
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>60514611700</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D85" s="55" t="inlineStr">
@@ -14996,15 +15043,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Y85" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z85" s="54" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="55" t="inlineStr">
         <is>
@@ -15021,18 +15064,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD85" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="AE85" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="AF85" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AG85" s="55" t="inlineStr">
         <is>
@@ -15054,27 +15093,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL85" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK85" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL85" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="AM85" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN85" s="43" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -15084,7 +15119,7 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>57982471000</t>
+          <t>57206773929</t>
         </is>
       </c>
       <c r="D86" s="35" t="inlineStr">
@@ -15117,13 +15152,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J86" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J86" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L86" s="36" t="inlineStr">
         <is>
@@ -15140,18 +15175,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O86" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P86" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O86" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="46" t="n">
+        <v>2</v>
       </c>
       <c r="Q86" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R86" s="37" t="inlineStr">
         <is>
@@ -15168,35 +15199,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U86" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U86" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W86" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X86" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W86" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X86" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Y86" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z86" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z86" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="38" t="inlineStr">
         <is>
@@ -15213,13 +15236,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD86" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD86" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AE86" s="40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF86" s="41" t="inlineStr">
         <is>
@@ -15257,7 +15278,7 @@
         </is>
       </c>
       <c r="AM86" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN86" s="43" t="n">
         <v>5</v>
@@ -15266,7 +15287,7 @@
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
-          <t>Isaac Zuñiga Silgado</t>
+          <t>Maria Fernanda Medina Reyes</t>
         </is>
       </c>
       <c r="B87" s="52" t="inlineStr">
@@ -15276,7 +15297,7 @@
       </c>
       <c r="C87" s="52" t="inlineStr">
         <is>
-          <t>60157655200</t>
+          <t>57221229836</t>
         </is>
       </c>
       <c r="D87" s="55" t="inlineStr">
@@ -15284,10 +15305,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E87" s="54" t="n">
+        <v>1</v>
       </c>
       <c r="F87" s="55" t="inlineStr">
         <is>
@@ -15304,15 +15323,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I87" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="K87" s="55" t="inlineStr">
         <is>
@@ -15359,10 +15374,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T87" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="55" t="inlineStr">
         <is>
@@ -15374,25 +15387,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W87" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="Y87" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z87" s="54" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="55" t="inlineStr">
         <is>
@@ -15409,13 +15416,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD87" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD87" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="AE87" s="57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF87" s="55" t="inlineStr">
         <is>
@@ -15453,205 +15458,1169 @@
         </is>
       </c>
       <c r="AM87" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN87" s="43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
+          <t>Misorly del Carmen Soto Acevedo</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C88" s="34" t="inlineStr">
+        <is>
+          <t>58523088300</t>
+        </is>
+      </c>
+      <c r="D88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O88" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P88" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X88" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM88" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN88" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>Jairo Enrique Serrano Castañeda</t>
+        </is>
+      </c>
+      <c r="B89" s="52" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C89" s="52" t="inlineStr">
+        <is>
+          <t>57220927199</t>
+        </is>
+      </c>
+      <c r="D89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q89" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X89" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE89" s="57" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK89" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL89" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM89" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="43" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>Julio Antonio Gomez Mora</t>
+        </is>
+      </c>
+      <c r="B90" s="34" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C90" s="34" t="inlineStr">
+        <is>
+          <t>60514611700</t>
+        </is>
+      </c>
+      <c r="D90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q90" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X90" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD90" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE90" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL90" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM90" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>Yuranis Henriquez Nuñez</t>
+        </is>
+      </c>
+      <c r="B91" s="52" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C91" s="52" t="inlineStr">
+        <is>
+          <t>57982471000</t>
+        </is>
+      </c>
+      <c r="D91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J91" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q91" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE91" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL91" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM91" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>Isaac Zuñiga Silgado</t>
+        </is>
+      </c>
+      <c r="B92" s="34" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C92" s="34" t="inlineStr">
+        <is>
+          <t>60157655200</t>
+        </is>
+      </c>
+      <c r="D92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q92" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X92" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE92" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL92" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM92" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
           <t>Marelbi del Carmen Olmos Perez</t>
         </is>
       </c>
-      <c r="B88" s="34" t="inlineStr">
+      <c r="B93" s="52" t="inlineStr">
         <is>
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C88" s="34" t="inlineStr">
+      <c r="C93" s="52" t="inlineStr">
         <is>
           <t>58868256900</t>
         </is>
       </c>
-      <c r="D88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P88" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q88" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X88" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM88" s="42" t="n">
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q93" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM93" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="AN88" s="43" t="n">
+      <c r="AN93" s="43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15660,10 +16629,10 @@
     <mergeCell ref="Y1:AE1"/>
     <mergeCell ref="A3:AN3"/>
     <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A78:AN78"/>
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="A57:AN57"/>
-    <mergeCell ref="A73:AN73"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A5:AN5"/>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Autores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pivot Autores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -375,13 +375,13 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN97"/>
+  <dimension ref="A1:AN99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" s="49" t="n">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AF7" s="49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG7" s="48" t="inlineStr">
         <is>
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="AK7" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL7" s="51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM7" s="44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN7" s="45" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -1956,7 +1956,7 @@
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Jorge Luis Muñiz Olite</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>55649334800</t>
+          <t>57758796500</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
@@ -1975,12 +1975,10 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G10" s="35" t="inlineStr">
         <is>
@@ -1993,25 +1991,21 @@
         </is>
       </c>
       <c r="I10" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L10" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M10" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="N10" s="38" t="inlineStr">
         <is>
@@ -2023,13 +2017,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P10" s="54" t="n">
+        <v>2</v>
       </c>
       <c r="Q10" s="55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" s="39" t="inlineStr">
         <is>
@@ -2041,10 +2033,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T10" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="39" t="inlineStr">
         <is>
@@ -2056,16 +2046,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W10" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X10" s="57" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="22" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Y10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z10" s="40" t="inlineStr">
         <is>
@@ -2087,14 +2077,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD10" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF10" s="27" t="n">
-        <v>1</v>
+      <c r="AD10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG10" s="43" t="inlineStr">
         <is>
@@ -2116,23 +2112,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK10" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="59" t="n">
-        <v>2</v>
+      <c r="AK10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM10" s="44" t="n">
         <v>5</v>
       </c>
       <c r="AN10" s="45" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Muñiz Olite</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="B11" s="47" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C11" s="47" t="inlineStr">
         <is>
-          <t>57758796500</t>
+          <t>55649334800</t>
         </is>
       </c>
       <c r="D11" s="48" t="inlineStr">
@@ -2151,10 +2151,12 @@
         </is>
       </c>
       <c r="E11" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="58" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G11" s="48" t="inlineStr">
         <is>
@@ -2167,21 +2169,25 @@
         </is>
       </c>
       <c r="I11" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="49" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L11" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M11" s="58" t="n">
-        <v>1</v>
+      <c r="M11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N11" s="48" t="inlineStr">
         <is>
@@ -2193,11 +2199,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P11" s="50" t="n">
-        <v>2</v>
+      <c r="P11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q11" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" s="48" t="inlineStr">
         <is>
@@ -2209,8 +2217,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T11" s="58" t="n">
-        <v>1</v>
+      <c r="T11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U11" s="48" t="inlineStr">
         <is>
@@ -2222,16 +2232,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W11" s="50" t="n">
-        <v>1</v>
+      <c r="W11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X11" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Y11" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Z11" s="48" t="inlineStr">
         <is>
@@ -2253,15 +2263,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD11" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="51" t="n">
+        <v>7</v>
       </c>
       <c r="AF11" s="48" t="inlineStr">
         <is>
@@ -2293,16 +2299,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL11" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM11" s="44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="45" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -3089,7 +3093,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="60" t="n">
+      <c r="H16" s="59" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="36" t="n">
@@ -4305,7 +4309,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V24" s="61" t="n">
+      <c r="V24" s="60" t="n">
         <v>1</v>
       </c>
       <c r="W24" s="56" t="n">
@@ -4367,7 +4371,7 @@
       <c r="AK24" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL24" s="59" t="n">
+      <c r="AL24" s="61" t="n">
         <v>1</v>
       </c>
       <c r="AM24" s="44" t="n">
@@ -4699,7 +4703,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL26" s="59" t="n">
+      <c r="AL26" s="61" t="n">
         <v>1</v>
       </c>
       <c r="AM26" s="44" t="n">
@@ -5377,7 +5381,7 @@
       <c r="AK30" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL30" s="59" t="n">
+      <c r="AL30" s="61" t="n">
         <v>1</v>
       </c>
       <c r="AM30" s="44" t="n">
@@ -6089,7 +6093,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL34" s="59" t="n">
+      <c r="AL34" s="61" t="n">
         <v>1</v>
       </c>
       <c r="AM34" s="44" t="n">
@@ -7949,7 +7953,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL44" s="59" t="n">
+      <c r="AL44" s="61" t="n">
         <v>1</v>
       </c>
       <c r="AM44" s="44" t="n">
@@ -10274,7 +10278,7 @@
     <row r="57">
       <c r="A57" s="46" t="inlineStr">
         <is>
-          <t>Luz Alejandra Magre Colorado</t>
+          <t>Luis Carlos Arraut Camargo</t>
         </is>
       </c>
       <c r="B57" s="47" t="inlineStr">
@@ -10284,7 +10288,7 @@
       </c>
       <c r="C57" s="47" t="inlineStr">
         <is>
-          <t>56682785300</t>
+          <t>58153979500</t>
         </is>
       </c>
       <c r="D57" s="48" t="inlineStr">
@@ -10318,7 +10322,7 @@
         </is>
       </c>
       <c r="J57" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="48" t="inlineStr">
         <is>
@@ -10464,172 +10468,210 @@
         <v>0</v>
       </c>
       <c r="AN57" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
-        </is>
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>Luz Alejandra Magre Colorado</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>56682785300</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X58" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE58" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL58" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM58" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
-        <is>
-          <t>Pedro Vazquez Miraz</t>
-        </is>
-      </c>
-      <c r="B59" s="47" t="inlineStr">
-        <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
-        </is>
-      </c>
-      <c r="C59" s="47" t="inlineStr">
-        <is>
-          <t>57196040759</t>
-        </is>
-      </c>
-      <c r="D59" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="K59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L59" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N59" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P59" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q59" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R59" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T59" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="U59" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="V59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W59" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="X59" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA59" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD59" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE59" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG59" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI59" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK59" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL59" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM59" s="44" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN59" s="45" t="n">
-        <v>18</v>
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -10780,7 +10822,7 @@
       <c r="AK60" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="AL60" s="59" t="n">
+      <c r="AL60" s="61" t="n">
         <v>2</v>
       </c>
       <c r="AM60" s="44" t="n">
@@ -10793,7 +10835,7 @@
     <row r="61">
       <c r="A61" s="46" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="B61" s="47" t="inlineStr">
@@ -10803,84 +10845,76 @@
       </c>
       <c r="C61" s="47" t="inlineStr">
         <is>
-          <t>57223851529</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="D61" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="58" t="n">
+      <c r="E61" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S61" s="52" t="n">
-        <v>1</v>
+      <c r="Q61" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R61" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="T61" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U61" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" s="48" t="inlineStr">
         <is>
@@ -10888,13 +10922,15 @@
         </is>
       </c>
       <c r="W61" s="50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X61" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y61" s="49" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="Y61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z61" s="48" t="inlineStr">
         <is>
@@ -10902,7 +10938,7 @@
         </is>
       </c>
       <c r="AA61" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB61" s="48" t="inlineStr">
         <is>
@@ -10918,18 +10954,16 @@
         <v>2</v>
       </c>
       <c r="AE61" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG61" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="AF61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AH61" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -10945,27 +10979,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK61" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL61" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AM61" s="44" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AN61" s="45" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
@@ -10975,26 +11005,24 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>58145499200</t>
-        </is>
-      </c>
-      <c r="D62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57223851529</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="n">
-        <v>1</v>
+      <c r="F62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H62" s="35" t="inlineStr">
         <is>
@@ -11002,13 +11030,15 @@
         </is>
       </c>
       <c r="I62" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L62" s="38" t="inlineStr">
         <is>
@@ -11030,77 +11060,73 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P62" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="55" t="n">
-        <v>1</v>
+      <c r="P62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R62" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V62" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W62" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="X62" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="Y62" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA62" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD62" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="Z62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA62" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD62" s="41" t="n">
-        <v>3</v>
-      </c>
       <c r="AE62" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF62" s="27" t="n">
         <v>2</v>
       </c>
+      <c r="AF62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="AG62" s="43" t="inlineStr">
         <is>
           <t>—</t>
@@ -11121,23 +11147,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK62" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL62" s="59" t="n">
-        <v>2</v>
+      <c r="AK62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM62" s="44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN62" s="45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="B63" s="47" t="inlineStr">
@@ -11147,7 +11177,7 @@
       </c>
       <c r="C63" s="47" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>58145499200</t>
         </is>
       </c>
       <c r="D63" s="48" t="inlineStr">
@@ -11165,38 +11195,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G63" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I63" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="L63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M63" s="58" t="n">
-        <v>1</v>
+      <c r="M63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N63" s="48" t="inlineStr">
         <is>
@@ -11224,61 +11248,61 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T63" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" s="53" t="n">
-        <v>1</v>
+      <c r="T63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W63" s="50" t="n">
+      <c r="W63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y63" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="X63" s="51" t="n">
+      <c r="Z63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA63" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD63" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE63" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF63" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="Y63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF63" s="49" t="n">
-        <v>1</v>
-      </c>
       <c r="AG63" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -11300,22 +11324,22 @@
         </is>
       </c>
       <c r="AK63" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL63" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM63" s="44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN63" s="45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>William Arellano Cartagena</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -11325,7 +11349,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>58068069000</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -11333,8 +11357,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="8" t="n">
-        <v>1</v>
+      <c r="E64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
@@ -11351,11 +11377,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="37" t="n">
-        <v>1</v>
+      <c r="I64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
@@ -11396,10 +11426,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T64" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T64" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="20" t="n">
         <v>1</v>
@@ -11410,10 +11438,10 @@
         </is>
       </c>
       <c r="W64" s="56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X64" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y64" s="40" t="inlineStr">
         <is>
@@ -11430,24 +11458,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB64" s="25" t="n">
-        <v>1</v>
+      <c r="AB64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD64" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE64" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF64" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG64" s="43" t="inlineStr">
         <is>
@@ -11469,15 +11501,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK64" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL64" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="AM64" s="44" t="n">
         <v>4</v>
@@ -11489,7 +11517,7 @@
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>William Arellano Cartagena</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -11499,7 +11527,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>58068069000</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -11507,10 +11535,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E65" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F65" s="48" t="inlineStr">
         <is>
@@ -11527,15 +11553,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I65" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K65" s="48" t="inlineStr">
         <is>
@@ -11581,41 +11603,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U65" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W65" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X65" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z65" s="52" t="n">
-        <v>2</v>
+      <c r="Z65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AB65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB65" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC65" s="48" t="inlineStr">
         <is>
@@ -11623,10 +11641,10 @@
         </is>
       </c>
       <c r="AD65" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF65" s="48" t="inlineStr">
         <is>
@@ -11638,8 +11656,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH65" s="58" t="n">
-        <v>1</v>
+      <c r="AH65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI65" s="48" t="inlineStr">
         <is>
@@ -11651,23 +11671,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL65" s="51" t="n">
-        <v>1</v>
+      <c r="AK65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM65" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN65" s="45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -11677,7 +11701,7 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -11725,13 +11749,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="15" t="n">
-        <v>1</v>
+      <c r="M66" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O66" s="38" t="inlineStr">
         <is>
@@ -11774,23 +11798,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X66" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X66" s="57" t="n">
+        <v>4</v>
       </c>
       <c r="Y66" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA66" s="24" t="n">
-        <v>1</v>
+      <c r="Z66" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB66" s="40" t="inlineStr">
         <is>
@@ -11803,43 +11825,51 @@
         </is>
       </c>
       <c r="AD66" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE66" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF66" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG66" s="28" t="n">
-        <v>1</v>
+      <c r="AG66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH66" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI66" s="30" t="n">
-        <v>1</v>
+      <c r="AI66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ66" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK66" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL66" s="59" t="n">
-        <v>2</v>
+      <c r="AK66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM66" s="44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN66" s="45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -12207,7 +12237,7 @@
     <row r="69">
       <c r="A69" s="46" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B69" s="47" t="inlineStr">
@@ -12217,7 +12247,7 @@
       </c>
       <c r="C69" s="47" t="inlineStr">
         <is>
-          <t>57392556500</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D69" s="48" t="inlineStr">
@@ -12255,8 +12285,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K69" s="49" t="n">
-        <v>1</v>
+      <c r="K69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L69" s="48" t="inlineStr">
         <is>
@@ -12268,10 +12300,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N69" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O69" s="48" t="inlineStr">
         <is>
@@ -12314,8 +12344,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X69" s="51" t="n">
-        <v>4</v>
+      <c r="X69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y69" s="48" t="inlineStr">
         <is>
@@ -12327,10 +12359,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA69" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AB69" s="48" t="inlineStr">
         <is>
@@ -12342,13 +12372,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD69" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="AE69" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF69" s="48" t="inlineStr">
         <is>
@@ -12380,16 +12408,16 @@
         <v>1</v>
       </c>
       <c r="AM69" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN69" s="45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>Armando Jose Mercado Vega</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -12399,11 +12427,13 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>57824284000</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>1</v>
+          <t>57392556500</t>
+        </is>
+      </c>
+      <c r="D70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
@@ -12425,16 +12455,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I70" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L70" s="38" t="inlineStr">
         <is>
@@ -12456,15 +12488,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P70" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q70" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P70" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R70" s="39" t="inlineStr">
         <is>
@@ -12476,8 +12504,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T70" s="19" t="n">
-        <v>1</v>
+      <c r="T70" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U70" s="39" t="inlineStr">
         <is>
@@ -12489,11 +12519,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W70" s="56" t="n">
-        <v>1</v>
+      <c r="W70" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X70" s="57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y70" s="40" t="inlineStr">
         <is>
@@ -12525,20 +12557,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE70" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE70" s="42" t="n">
+        <v>4</v>
       </c>
       <c r="AF70" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG70" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG70" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH70" s="43" t="inlineStr">
         <is>
@@ -12555,27 +12583,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK70" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL70" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK70" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL70" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="AM70" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN70" s="45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="46" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Armando Jose Mercado Vega</t>
         </is>
       </c>
       <c r="B71" s="47" t="inlineStr">
@@ -12585,16 +12609,16 @@
       </c>
       <c r="C71" s="47" t="inlineStr">
         <is>
-          <t>57204842254</t>
-        </is>
-      </c>
-      <c r="D71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="52" t="n">
-        <v>1</v>
+          <t>57824284000</t>
+        </is>
+      </c>
+      <c r="D71" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F71" s="48" t="inlineStr">
         <is>
@@ -12662,10 +12686,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T71" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="U71" s="48" t="inlineStr">
         <is>
@@ -12677,23 +12699,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y71" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z71" s="52" t="n">
-        <v>1</v>
+      <c r="Z71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA71" s="48" t="inlineStr">
         <is>
@@ -12710,11 +12730,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD71" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE71" s="51" t="n">
-        <v>1</v>
+      <c r="AD71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF71" s="48" t="inlineStr">
         <is>
@@ -12761,7 +12785,7 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
@@ -12771,7 +12795,7 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>58620428800</t>
+          <t>57204842254</t>
         </is>
       </c>
       <c r="D72" s="35" t="inlineStr">
@@ -12779,10 +12803,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E72" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
@@ -12799,10 +12821,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I72" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="J72" s="37" t="n">
         <v>1</v>
@@ -12822,19 +12842,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N72" s="15" t="n">
-        <v>1</v>
+      <c r="N72" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O72" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P72" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="55" t="n">
-        <v>2</v>
+      <c r="P72" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R72" s="39" t="inlineStr">
         <is>
@@ -12866,8 +12892,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X72" s="57" t="n">
-        <v>4</v>
+      <c r="X72" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y72" s="40" t="inlineStr">
         <is>
@@ -12896,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="AE72" s="42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF72" s="43" t="inlineStr">
         <is>
@@ -12937,13 +12965,13 @@
         <v>2</v>
       </c>
       <c r="AN72" s="45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="46" t="inlineStr">
         <is>
-          <t>Rita Cecilia de la Hoz del Villar</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="B73" s="47" t="inlineStr">
@@ -12953,7 +12981,7 @@
       </c>
       <c r="C73" s="47" t="inlineStr">
         <is>
-          <t>59326410200</t>
+          <t>58620428800</t>
         </is>
       </c>
       <c r="D73" s="48" t="inlineStr">
@@ -12986,10 +13014,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K73" s="48" t="inlineStr">
         <is>
@@ -13006,25 +13032,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N73" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="R73" s="48" t="inlineStr">
         <is>
@@ -13057,7 +13077,7 @@
         </is>
       </c>
       <c r="X73" s="51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y73" s="48" t="inlineStr">
         <is>
@@ -13124,16 +13144,16 @@
         </is>
       </c>
       <c r="AM73" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN73" s="45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Roman Melendez</t>
+          <t>Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -13143,7 +13163,7 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>56006978600</t>
+          <t>59326410200</t>
         </is>
       </c>
       <c r="D74" s="35" t="inlineStr">
@@ -13196,19 +13216,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N74" s="15" t="n">
-        <v>1</v>
+      <c r="N74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O74" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P74" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="55" t="n">
-        <v>1</v>
+      <c r="P74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R74" s="39" t="inlineStr">
         <is>
@@ -13240,20 +13266,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X74" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X74" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="Y74" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z74" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z74" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="40" t="inlineStr">
         <is>
@@ -13270,15 +13292,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD74" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE74" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD74" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="AF74" s="43" t="inlineStr">
         <is>
@@ -13319,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AN74" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -13517,7 +13535,7 @@
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>Daniel Toro Gonzalez</t>
+          <t>Augusto Andres Alean Romero</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
@@ -13527,11 +13545,13 @@
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>56380539800</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>1</v>
+          <t>58954857900</t>
+        </is>
+      </c>
+      <c r="D76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
@@ -13553,11 +13573,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I76" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="37" t="n">
-        <v>1</v>
+      <c r="I76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K76" s="38" t="inlineStr">
         <is>
@@ -13594,10 +13618,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R76" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R76" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="S76" s="39" t="inlineStr">
         <is>
@@ -13619,15 +13641,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W76" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X76" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W76" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="Y76" s="40" t="inlineStr">
         <is>
@@ -13709,7 +13727,7 @@
     <row r="77">
       <c r="A77" s="46" t="inlineStr">
         <is>
-          <t>Alba Zulay Cardenas Escobar</t>
+          <t>Gabriel Roman Melendez</t>
         </is>
       </c>
       <c r="B77" s="47" t="inlineStr">
@@ -13719,7 +13737,7 @@
       </c>
       <c r="C77" s="47" t="inlineStr">
         <is>
-          <t>57930948900</t>
+          <t>56006978600</t>
         </is>
       </c>
       <c r="D77" s="48" t="inlineStr">
@@ -13752,8 +13770,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J77" s="51" t="n">
-        <v>4</v>
+      <c r="J77" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K77" s="48" t="inlineStr">
         <is>
@@ -13770,23 +13790,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N77" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N77" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O77" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P77" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P77" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="Q77" s="51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R77" s="48" t="inlineStr">
         <is>
@@ -13818,8 +13834,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X77" s="51" t="n">
-        <v>4</v>
+      <c r="X77" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y77" s="48" t="inlineStr">
         <is>
@@ -13851,8 +13869,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE77" s="51" t="n">
-        <v>6</v>
+      <c r="AE77" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF77" s="48" t="inlineStr">
         <is>
@@ -13890,16 +13910,16 @@
         </is>
       </c>
       <c r="AM77" s="44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN77" s="45" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo</t>
+          <t>Daniel Toro Gonzalez</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
@@ -13909,13 +13929,11 @@
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>59326202000</t>
-        </is>
-      </c>
-      <c r="D78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>56380539800</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E78" s="35" t="inlineStr">
         <is>
@@ -13937,15 +13955,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I78" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K78" s="38" t="inlineStr">
         <is>
@@ -14012,8 +14026,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X78" s="57" t="n">
-        <v>3</v>
+      <c r="X78" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y78" s="40" t="inlineStr">
         <is>
@@ -14045,8 +14061,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE78" s="42" t="n">
-        <v>3</v>
+      <c r="AE78" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF78" s="43" t="inlineStr">
         <is>
@@ -14084,16 +14102,16 @@
         </is>
       </c>
       <c r="AM78" s="44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN78" s="45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="46" t="inlineStr">
         <is>
-          <t>Juan Camilo Medellin Rojas</t>
+          <t>Alba Zulay Cardenas Escobar</t>
         </is>
       </c>
       <c r="B79" s="47" t="inlineStr">
@@ -14103,7 +14121,7 @@
       </c>
       <c r="C79" s="47" t="inlineStr">
         <is>
-          <t>60150905000</t>
+          <t>57930948900</t>
         </is>
       </c>
       <c r="D79" s="48" t="inlineStr">
@@ -14136,10 +14154,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J79" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="K79" s="48" t="inlineStr">
         <is>
@@ -14171,10 +14187,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q79" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q79" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="R79" s="48" t="inlineStr">
         <is>
@@ -14206,10 +14220,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X79" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X79" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="Y79" s="48" t="inlineStr">
         <is>
@@ -14242,7 +14254,7 @@
         </is>
       </c>
       <c r="AE79" s="51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF79" s="48" t="inlineStr">
         <is>
@@ -14283,13 +14295,13 @@
         <v>0</v>
       </c>
       <c r="AN79" s="45" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>Martha Patricia Castro Porto</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -14299,7 +14311,7 @@
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
-          <t>58928816700</t>
+          <t>59326202000</t>
         </is>
       </c>
       <c r="D80" s="35" t="inlineStr">
@@ -14367,8 +14379,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q80" s="55" t="n">
-        <v>1</v>
+      <c r="Q80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R80" s="39" t="inlineStr">
         <is>
@@ -14401,7 +14415,7 @@
         </is>
       </c>
       <c r="X80" s="57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y80" s="40" t="inlineStr">
         <is>
@@ -14433,10 +14447,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE80" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE80" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="AF80" s="43" t="inlineStr">
         <is>
@@ -14477,328 +14489,410 @@
         <v>0</v>
       </c>
       <c r="AN80" s="45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
-        </is>
+      <c r="A81" s="46" t="inlineStr">
+        <is>
+          <t>Juan Camilo Medellin Rojas</t>
+        </is>
+      </c>
+      <c r="B81" s="47" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C81" s="47" t="inlineStr">
+        <is>
+          <t>60150905000</t>
+        </is>
+      </c>
+      <c r="D81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE81" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL81" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM81" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Martha Patricia Castro Porto</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C82" s="34" t="inlineStr">
         <is>
-          <t>57191333650</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="8" t="n">
+          <t>58928816700</t>
+        </is>
+      </c>
+      <c r="D82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q82" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W82" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X82" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE82" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL82" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM82" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN82" s="45" t="n">
         <v>2</v>
-      </c>
-      <c r="F82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="54" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q82" s="55" t="n">
-        <v>6</v>
-      </c>
-      <c r="R82" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W82" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="X82" s="57" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y82" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z82" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD82" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE82" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF82" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG82" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH82" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK82" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL82" s="59" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM82" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN82" s="45" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="46" t="inlineStr">
-        <is>
-          <t>Miguel Efren Garces Prettel</t>
-        </is>
-      </c>
-      <c r="B83" s="47" t="inlineStr">
-        <is>
-          <t>Escuela de Transformación Digital</t>
-        </is>
-      </c>
-      <c r="C83" s="47" t="inlineStr">
-        <is>
-          <t>57193012270</t>
-        </is>
-      </c>
-      <c r="D83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P83" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="R83" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="S83" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U83" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W83" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="X83" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD83" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE83" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF83" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG83" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH83" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK83" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL83" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM83" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN83" s="45" t="n">
-        <v>20</v>
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -14808,16 +14902,14 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>57191333650</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E84" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="F84" s="35" t="inlineStr">
         <is>
@@ -14835,108 +14927,98 @@
         </is>
       </c>
       <c r="I84" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="54" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q84" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="R84" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="L84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P84" s="54" t="n">
+      <c r="S84" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W84" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="X84" s="57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y84" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z84" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA84" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB84" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC84" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD84" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE84" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF84" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="R84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S84" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T84" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U84" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V84" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W84" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD84" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF84" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG84" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH84" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="AI84" s="43" t="inlineStr">
         <is>
@@ -14949,13 +15031,13 @@
         </is>
       </c>
       <c r="AK84" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL84" s="59" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AL84" s="61" t="n">
+        <v>6</v>
       </c>
       <c r="AM84" s="44" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AN84" s="45" t="n">
         <v>31</v>
@@ -14964,7 +15046,7 @@
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
@@ -14974,21 +15056,19 @@
       </c>
       <c r="C85" s="47" t="inlineStr">
         <is>
-          <t>57202285682</t>
-        </is>
-      </c>
-      <c r="D85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57193012270</t>
+        </is>
+      </c>
+      <c r="D85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="G85" s="48" t="inlineStr">
         <is>
@@ -15001,111 +15081,99 @@
         </is>
       </c>
       <c r="I85" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P85" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R85" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P85" s="50" t="n">
+      <c r="S85" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U85" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W85" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="X85" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y85" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD85" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="Q85" s="51" t="n">
-        <v>12</v>
-      </c>
-      <c r="R85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X85" s="51" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD85" s="50" t="n">
+      <c r="AF85" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG85" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH85" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="AE85" s="51" t="n">
-        <v>31</v>
-      </c>
-      <c r="AF85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AI85" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -15117,22 +15185,22 @@
         </is>
       </c>
       <c r="AK85" s="50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AL85" s="51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM85" s="44" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AN85" s="45" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -15142,13 +15210,11 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>26325154200</t>
-        </is>
-      </c>
-      <c r="D86" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57156565000</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E86" s="35" t="inlineStr">
         <is>
@@ -15170,24 +15236,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I86" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="J86" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L86" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="N86" s="38" t="inlineStr">
         <is>
@@ -15200,15 +15264,13 @@
         </is>
       </c>
       <c r="P86" s="54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q86" s="55" t="n">
-        <v>14</v>
-      </c>
-      <c r="R86" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R86" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="S86" s="39" t="inlineStr">
         <is>
@@ -15230,10 +15292,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W86" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W86" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X86" s="57" t="n">
         <v>15</v>
@@ -15241,8 +15301,10 @@
       <c r="Y86" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" s="23" t="n">
-        <v>1</v>
+      <c r="Z86" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA86" s="40" t="inlineStr">
         <is>
@@ -15260,13 +15322,15 @@
         </is>
       </c>
       <c r="AD86" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE86" s="42" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF86" s="27" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AF86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG86" s="43" t="inlineStr">
         <is>
@@ -15288,23 +15352,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK86" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL86" s="59" t="n">
-        <v>4</v>
+      <c r="AK86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM86" s="44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN86" s="45" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="46" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="B87" s="47" t="inlineStr">
@@ -15314,16 +15382,16 @@
       </c>
       <c r="C87" s="47" t="inlineStr">
         <is>
-          <t>57216868622</t>
-        </is>
-      </c>
-      <c r="D87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="52" t="n">
-        <v>1</v>
+          <t>57202285682</t>
+        </is>
+      </c>
+      <c r="D87" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F87" s="48" t="inlineStr">
         <is>
@@ -15344,36 +15412,34 @@
         <v>1</v>
       </c>
       <c r="J87" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M87" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P87" s="50" t="n">
-        <v>1</v>
-      </c>
       <c r="Q87" s="51" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R87" s="48" t="inlineStr">
         <is>
@@ -15405,18 +15471,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X87" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y87" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Z87" s="52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA87" s="48" t="inlineStr">
         <is>
@@ -15434,15 +15496,13 @@
         </is>
       </c>
       <c r="AD87" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE87" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="AF87" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="AG87" s="48" t="inlineStr">
         <is>
@@ -15464,27 +15524,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL87" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AM87" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN87" s="45" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -15494,7 +15550,7 @@
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>26325154200</t>
         </is>
       </c>
       <c r="D88" s="35" t="inlineStr">
@@ -15527,20 +15583,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J88" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="M88" s="38" t="inlineStr">
         <is>
@@ -15557,15 +15607,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P88" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" s="55" t="n">
+        <v>14</v>
       </c>
       <c r="R88" s="39" t="inlineStr">
         <is>
@@ -15597,37 +15643,35 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X88" s="57" t="n">
+        <v>15</v>
       </c>
       <c r="Y88" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD88" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="Z88" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD88" s="41" t="n">
-        <v>3</v>
-      </c>
       <c r="AE88" s="42" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AF88" s="27" t="n">
         <v>1</v>
@@ -15655,20 +15699,20 @@
       <c r="AK88" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL88" s="59" t="n">
-        <v>1</v>
+      <c r="AL88" s="61" t="n">
+        <v>4</v>
       </c>
       <c r="AM88" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN88" s="45" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="46" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="B89" s="47" t="inlineStr">
@@ -15678,7 +15722,7 @@
       </c>
       <c r="C89" s="47" t="inlineStr">
         <is>
-          <t>57206773929</t>
+          <t>57216868622</t>
         </is>
       </c>
       <c r="D89" s="48" t="inlineStr">
@@ -15686,10 +15730,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E89" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F89" s="48" t="inlineStr">
         <is>
@@ -15706,42 +15748,40 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K89" s="49" t="n">
-        <v>1</v>
+      <c r="I89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L89" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M89" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="N89" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O89" s="62" t="n">
-        <v>1</v>
+      <c r="O89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P89" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R89" s="48" t="inlineStr">
         <is>
@@ -15758,19 +15798,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U89" s="53" t="n">
-        <v>1</v>
+      <c r="U89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V89" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W89" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X89" s="51" t="n">
-        <v>1</v>
+      <c r="W89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y89" s="48" t="inlineStr">
         <is>
@@ -15778,7 +15824,7 @@
         </is>
       </c>
       <c r="Z89" s="52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA89" s="48" t="inlineStr">
         <is>
@@ -15796,10 +15842,10 @@
         </is>
       </c>
       <c r="AD89" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE89" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF89" s="48" t="inlineStr">
         <is>
@@ -15837,16 +15883,16 @@
         </is>
       </c>
       <c r="AM89" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN89" s="45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -15856,7 +15902,7 @@
       </c>
       <c r="C90" s="34" t="inlineStr">
         <is>
-          <t>57221229836</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D90" s="35" t="inlineStr">
@@ -15864,8 +15910,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E90" s="8" t="n">
-        <v>1</v>
+      <c r="E90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F90" s="35" t="inlineStr">
         <is>
@@ -15882,11 +15930,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I90" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="37" t="n">
-        <v>1</v>
+      <c r="I90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K90" s="38" t="inlineStr">
         <is>
@@ -15933,8 +15985,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T90" s="19" t="n">
-        <v>1</v>
+      <c r="T90" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U90" s="39" t="inlineStr">
         <is>
@@ -15946,16 +16000,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W90" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X90" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y90" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W90" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X90" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y90" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="Z90" s="23" t="n">
         <v>1</v>
@@ -15976,15 +16032,13 @@
         </is>
       </c>
       <c r="AD90" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE90" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="AF90" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG90" s="43" t="inlineStr">
         <is>
@@ -16006,27 +16060,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK90" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="AM90" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN90" s="45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="46" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="B91" s="47" t="inlineStr">
@@ -16036,7 +16086,7 @@
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t>59325343900</t>
+          <t>57206773929</t>
         </is>
       </c>
       <c r="D91" s="48" t="inlineStr">
@@ -16074,10 +16124,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K91" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="L91" s="48" t="inlineStr">
         <is>
@@ -16094,20 +16142,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O91" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="48" t="inlineStr">
         <is>
@@ -16124,64 +16166,58 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U91" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V91" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W91" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X91" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z91" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD91" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE91" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="Y91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE91" s="51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF91" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG91" s="52" t="n">
-        <v>1</v>
+      <c r="AG91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH91" s="48" t="inlineStr">
         <is>
@@ -16198,23 +16234,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK91" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL91" s="51" t="n">
-        <v>1</v>
+      <c r="AK91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM91" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN91" s="45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>Misorly del Carmen Soto Acevedo</t>
+          <t>Maria Fernanda Medina Reyes</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -16224,7 +16264,7 @@
       </c>
       <c r="C92" s="34" t="inlineStr">
         <is>
-          <t>58523088300</t>
+          <t>57221229836</t>
         </is>
       </c>
       <c r="D92" s="35" t="inlineStr">
@@ -16232,10 +16272,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E92" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E92" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F92" s="35" t="inlineStr">
         <is>
@@ -16252,15 +16290,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I92" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J92" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I92" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K92" s="38" t="inlineStr">
         <is>
@@ -16272,8 +16306,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M92" s="14" t="n">
-        <v>1</v>
+      <c r="M92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N92" s="38" t="inlineStr">
         <is>
@@ -16285,11 +16321,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P92" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q92" s="55" t="n">
-        <v>1</v>
+      <c r="P92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q92" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R92" s="39" t="inlineStr">
         <is>
@@ -16301,10 +16341,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T92" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T92" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="39" t="inlineStr">
         <is>
@@ -16316,25 +16354,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W92" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X92" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W92" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X92" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="Y92" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z92" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z92" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="40" t="inlineStr">
         <is>
@@ -16351,15 +16383,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD92" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE92" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD92" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE92" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="AF92" s="43" t="inlineStr">
         <is>
@@ -16397,16 +16425,16 @@
         </is>
       </c>
       <c r="AM92" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN92" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="46" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Misorly del Carmen Soto Acevedo</t>
         </is>
       </c>
       <c r="B93" s="47" t="inlineStr">
@@ -16416,7 +16444,7 @@
       </c>
       <c r="C93" s="47" t="inlineStr">
         <is>
-          <t>57220927199</t>
+          <t>58523088300</t>
         </is>
       </c>
       <c r="D93" s="48" t="inlineStr">
@@ -16449,8 +16477,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J93" s="51" t="n">
-        <v>1</v>
+      <c r="J93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K93" s="48" t="inlineStr">
         <is>
@@ -16462,10 +16492,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M93" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="N93" s="48" t="inlineStr">
         <is>
@@ -16477,13 +16505,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P93" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="Q93" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R93" s="48" t="inlineStr">
         <is>
@@ -16515,8 +16541,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X93" s="51" t="n">
-        <v>2</v>
+      <c r="X93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y93" s="48" t="inlineStr">
         <is>
@@ -16548,8 +16576,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE93" s="51" t="n">
-        <v>22</v>
+      <c r="AE93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF93" s="48" t="inlineStr">
         <is>
@@ -16581,20 +16611,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL93" s="51" t="n">
-        <v>2</v>
+      <c r="AL93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM93" s="44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN93" s="45" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>Julio Antonio Gomez Mora</t>
+          <t>Humberto Manuel Marbello Peña</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -16604,7 +16636,7 @@
       </c>
       <c r="C94" s="34" t="inlineStr">
         <is>
-          <t>60514611700</t>
+          <t>59325343900</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
@@ -16707,10 +16739,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X94" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X94" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="Y94" s="40" t="inlineStr">
         <is>
@@ -16750,10 +16780,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG94" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG94" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH94" s="43" t="inlineStr">
         <is>
@@ -16770,27 +16798,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK94" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL94" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK94" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL94" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="AM94" s="44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN94" s="45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="46" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="B95" s="47" t="inlineStr">
@@ -16800,7 +16824,7 @@
       </c>
       <c r="C95" s="47" t="inlineStr">
         <is>
-          <t>57982471000</t>
+          <t>57220927199</t>
         </is>
       </c>
       <c r="D95" s="48" t="inlineStr">
@@ -16867,7 +16891,7 @@
         </is>
       </c>
       <c r="Q95" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R95" s="48" t="inlineStr">
         <is>
@@ -16899,10 +16923,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X95" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X95" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="Y95" s="48" t="inlineStr">
         <is>
@@ -16935,7 +16957,7 @@
         </is>
       </c>
       <c r="AE95" s="51" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AF95" s="48" t="inlineStr">
         <is>
@@ -16967,22 +16989,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL95" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL95" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AM95" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AN95" s="45" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>Isaac Zuñiga Silgado</t>
+          <t>Julio Antonio Gomez Mora</t>
         </is>
       </c>
       <c r="B96" s="34" t="inlineStr">
@@ -16992,7 +17012,7 @@
       </c>
       <c r="C96" s="34" t="inlineStr">
         <is>
-          <t>60157655200</t>
+          <t>60514611700</t>
         </is>
       </c>
       <c r="D96" s="35" t="inlineStr">
@@ -17178,7 +17198,7 @@
     <row r="97">
       <c r="A97" s="46" t="inlineStr">
         <is>
-          <t>Marelbi del Carmen Olmos Perez</t>
+          <t>Yuranis Henriquez Nuñez</t>
         </is>
       </c>
       <c r="B97" s="47" t="inlineStr">
@@ -17188,7 +17208,7 @@
       </c>
       <c r="C97" s="47" t="inlineStr">
         <is>
-          <t>58868256900</t>
+          <t>57982471000</t>
         </is>
       </c>
       <c r="D97" s="48" t="inlineStr">
@@ -17221,10 +17241,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J97" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J97" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K97" s="48" t="inlineStr">
         <is>
@@ -17324,10 +17342,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE97" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE97" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="AF97" s="48" t="inlineStr">
         <is>
@@ -17368,6 +17384,398 @@
         <v>0</v>
       </c>
       <c r="AN97" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>Isaac Zuñiga Silgado</t>
+        </is>
+      </c>
+      <c r="B98" s="34" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="inlineStr">
+        <is>
+          <t>60157655200</t>
+        </is>
+      </c>
+      <c r="D98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J98" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q98" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X98" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD98" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE98" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL98" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM98" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="46" t="inlineStr">
+        <is>
+          <t>Marelbi del Carmen Olmos Perez</t>
+        </is>
+      </c>
+      <c r="B99" s="47" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C99" s="47" t="inlineStr">
+        <is>
+          <t>58868256900</t>
+        </is>
+      </c>
+      <c r="D99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q99" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL99" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM99" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17376,16 +17784,16 @@
     <mergeCell ref="Y1:AE1"/>
     <mergeCell ref="A3:AN3"/>
     <mergeCell ref="A6:AN6"/>
+    <mergeCell ref="A83:AN83"/>
     <mergeCell ref="AM1:AN1"/>
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="R1:X1"/>
-    <mergeCell ref="A81:AN81"/>
+    <mergeCell ref="A59:AN59"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A23:AN23"/>
     <mergeCell ref="AF1:AL1"/>
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="A58:AN58"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -375,13 +375,13 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN99"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" s="49" t="n">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AF7" s="49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG7" s="48" t="inlineStr">
         <is>
@@ -1599,16 +1599,16 @@
         </is>
       </c>
       <c r="AK7" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL7" s="51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM7" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN7" s="45" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -1956,7 +1956,7 @@
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
-          <t>Jorge Luis Muñiz Olite</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>57758796500</t>
+          <t>55649334800</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
@@ -1975,10 +1975,12 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
         <is>
@@ -1991,148 +1993,146 @@
         </is>
       </c>
       <c r="I10" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W10" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X10" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD10" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK10" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="59" t="n">
         <v>2</v>
-      </c>
-      <c r="J10" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P10" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V10" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W10" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE10" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="AM10" s="44" t="n">
         <v>5</v>
       </c>
       <c r="AN10" s="45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="46" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Jorge Luis Muñiz Olite</t>
         </is>
       </c>
       <c r="B11" s="47" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C11" s="47" t="inlineStr">
         <is>
-          <t>55649334800</t>
+          <t>57758796500</t>
         </is>
       </c>
       <c r="D11" s="48" t="inlineStr">
@@ -2151,12 +2151,10 @@
         </is>
       </c>
       <c r="E11" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F11" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="G11" s="48" t="inlineStr">
         <is>
@@ -2169,25 +2167,21 @@
         </is>
       </c>
       <c r="I11" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K11" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="L11" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M11" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="N11" s="48" t="inlineStr">
         <is>
@@ -2199,13 +2193,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P11" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="Q11" s="51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" s="48" t="inlineStr">
         <is>
@@ -2217,10 +2209,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T11" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="48" t="inlineStr">
         <is>
@@ -2232,16 +2222,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W11" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W11" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X11" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="49" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z11" s="48" t="inlineStr">
         <is>
@@ -2263,11 +2253,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="51" t="n">
-        <v>7</v>
+      <c r="AD11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF11" s="48" t="inlineStr">
         <is>
@@ -2299,14 +2293,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL11" s="51" t="n">
-        <v>1</v>
+      <c r="AL11" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM11" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN11" s="45" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3093,7 +3089,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="59" t="n">
+      <c r="H16" s="60" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="36" t="n">
@@ -4309,7 +4305,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V24" s="60" t="n">
+      <c r="V24" s="61" t="n">
         <v>1</v>
       </c>
       <c r="W24" s="56" t="n">
@@ -4371,7 +4367,7 @@
       <c r="AK24" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL24" s="61" t="n">
+      <c r="AL24" s="59" t="n">
         <v>1</v>
       </c>
       <c r="AM24" s="44" t="n">
@@ -4703,7 +4699,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL26" s="61" t="n">
+      <c r="AL26" s="59" t="n">
         <v>1</v>
       </c>
       <c r="AM26" s="44" t="n">
@@ -5381,7 +5377,7 @@
       <c r="AK30" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL30" s="61" t="n">
+      <c r="AL30" s="59" t="n">
         <v>1</v>
       </c>
       <c r="AM30" s="44" t="n">
@@ -6093,7 +6089,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL34" s="61" t="n">
+      <c r="AL34" s="59" t="n">
         <v>1</v>
       </c>
       <c r="AM34" s="44" t="n">
@@ -7953,7 +7949,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL44" s="61" t="n">
+      <c r="AL44" s="59" t="n">
         <v>1</v>
       </c>
       <c r="AM44" s="44" t="n">
@@ -10278,7 +10274,7 @@
     <row r="57">
       <c r="A57" s="46" t="inlineStr">
         <is>
-          <t>Luis Carlos Arraut Camargo</t>
+          <t>Luz Alejandra Magre Colorado</t>
         </is>
       </c>
       <c r="B57" s="47" t="inlineStr">
@@ -10288,7 +10284,7 @@
       </c>
       <c r="C57" s="47" t="inlineStr">
         <is>
-          <t>58153979500</t>
+          <t>56682785300</t>
         </is>
       </c>
       <c r="D57" s="48" t="inlineStr">
@@ -10322,7 +10318,7 @@
         </is>
       </c>
       <c r="J57" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="48" t="inlineStr">
         <is>
@@ -10468,210 +10464,172 @@
         <v>0</v>
       </c>
       <c r="AN57" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="inlineStr">
-        <is>
-          <t>Luz Alejandra Magre Colorado</t>
-        </is>
-      </c>
-      <c r="B58" s="34" t="inlineStr">
-        <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
-        </is>
-      </c>
-      <c r="C58" s="34" t="inlineStr">
-        <is>
-          <t>56682785300</t>
-        </is>
-      </c>
-      <c r="D58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q58" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X58" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE58" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL58" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM58" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" s="45" t="n">
-        <v>1</v>
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
-        </is>
+      <c r="A59" s="46" t="inlineStr">
+        <is>
+          <t>Pedro Vazquez Miraz</t>
+        </is>
+      </c>
+      <c r="B59" s="47" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+      <c r="C59" s="47" t="inlineStr">
+        <is>
+          <t>57196040759</t>
+        </is>
+      </c>
+      <c r="D59" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P59" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T59" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="V59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W59" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="X59" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA59" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD59" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE59" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG59" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI59" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK59" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL59" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM59" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN59" s="45" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -10822,7 +10780,7 @@
       <c r="AK60" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="AL60" s="61" t="n">
+      <c r="AL60" s="59" t="n">
         <v>2</v>
       </c>
       <c r="AM60" s="44" t="n">
@@ -10835,7 +10793,7 @@
     <row r="61">
       <c r="A61" s="46" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="B61" s="47" t="inlineStr">
@@ -10845,76 +10803,84 @@
       </c>
       <c r="C61" s="47" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>57223851529</t>
         </is>
       </c>
       <c r="D61" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="52" t="n">
+      <c r="E61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="50" t="n">
-        <v>4</v>
-      </c>
       <c r="J61" s="51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L61" s="52" t="n">
-        <v>1</v>
+      <c r="L61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M61" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N61" s="53" t="n">
-        <v>1</v>
+      <c r="N61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O61" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P61" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S61" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="T61" s="58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U61" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61" s="48" t="inlineStr">
         <is>
@@ -10922,15 +10888,13 @@
         </is>
       </c>
       <c r="W61" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X61" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="Y61" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Z61" s="48" t="inlineStr">
         <is>
@@ -10938,7 +10902,7 @@
         </is>
       </c>
       <c r="AA61" s="58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB61" s="48" t="inlineStr">
         <is>
@@ -10954,15 +10918,17 @@
         <v>2</v>
       </c>
       <c r="AE61" s="51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF61" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG61" s="52" t="n">
-        <v>2</v>
+      <c r="AG61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH61" s="48" t="inlineStr">
         <is>
@@ -10979,23 +10945,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK61" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL61" s="51" t="n">
-        <v>2</v>
+      <c r="AK61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL61" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM61" s="44" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AN61" s="45" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
@@ -11005,169 +10975,169 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>57223851529</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>1</v>
+          <t>58145499200</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X62" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y62" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="G62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="36" t="n">
+      <c r="Z62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA62" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC62" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD62" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="J62" s="37" t="n">
+      <c r="AE62" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="K62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q62" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S62" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T62" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W62" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="X62" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA62" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD62" s="41" t="n">
+      <c r="AF62" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="AE62" s="42" t="n">
+      <c r="AG62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ62" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK62" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="AF62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL62" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL62" s="59" t="n">
+        <v>2</v>
       </c>
       <c r="AM62" s="44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN62" s="45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="46" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B63" s="47" t="inlineStr">
@@ -11177,7 +11147,7 @@
       </c>
       <c r="C63" s="47" t="inlineStr">
         <is>
-          <t>58145499200</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D63" s="48" t="inlineStr">
@@ -11195,32 +11165,38 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G63" s="53" t="n">
-        <v>1</v>
+      <c r="G63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I63" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="49" t="n">
-        <v>1</v>
+      <c r="I63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M63" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="N63" s="48" t="inlineStr">
         <is>
@@ -11248,41 +11224,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T63" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y63" s="49" t="n">
+      <c r="W63" s="50" t="n">
         <v>2</v>
       </c>
+      <c r="X63" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Z63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA63" s="58" t="n">
-        <v>1</v>
+      <c r="AA63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB63" s="48" t="inlineStr">
         <is>
@@ -11294,14 +11266,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD63" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE63" s="51" t="n">
-        <v>3</v>
+      <c r="AD63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF63" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG63" s="48" t="inlineStr">
         <is>
@@ -11324,22 +11300,22 @@
         </is>
       </c>
       <c r="AK63" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL63" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM63" s="44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AN63" s="45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>William Arellano Cartagena</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -11349,7 +11325,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>58068069000</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -11357,10 +11333,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E64" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
@@ -11377,15 +11351,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I64" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
@@ -11426,8 +11396,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T64" s="19" t="n">
-        <v>1</v>
+      <c r="T64" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U64" s="20" t="n">
         <v>1</v>
@@ -11438,10 +11410,10 @@
         </is>
       </c>
       <c r="W64" s="56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X64" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="40" t="inlineStr">
         <is>
@@ -11458,28 +11430,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB64" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB64" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD64" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE64" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF64" s="27" t="n">
-        <v>1</v>
+      <c r="AD64" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE64" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG64" s="43" t="inlineStr">
         <is>
@@ -11501,11 +11469,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK64" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL64" s="61" t="n">
-        <v>1</v>
+      <c r="AK64" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL64" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM64" s="44" t="n">
         <v>4</v>
@@ -11517,7 +11489,7 @@
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>William Arellano Cartagena</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -11527,7 +11499,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>58068069000</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -11535,8 +11507,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="52" t="n">
-        <v>1</v>
+      <c r="E65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F65" s="48" t="inlineStr">
         <is>
@@ -11553,11 +11527,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="51" t="n">
-        <v>1</v>
+      <c r="I65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K65" s="48" t="inlineStr">
         <is>
@@ -11603,37 +11581,41 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U65" s="53" t="n">
-        <v>1</v>
+      <c r="U65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W65" s="50" t="n">
-        <v>1</v>
+      <c r="W65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X65" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z65" s="52" t="n">
+        <v>2</v>
       </c>
       <c r="AA65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AB65" s="53" t="n">
-        <v>1</v>
+      <c r="AB65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC65" s="48" t="inlineStr">
         <is>
@@ -11641,10 +11623,10 @@
         </is>
       </c>
       <c r="AD65" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE65" s="51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF65" s="48" t="inlineStr">
         <is>
@@ -11656,10 +11638,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH65" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI65" s="48" t="inlineStr">
         <is>
@@ -11671,27 +11651,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK65" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL65" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM65" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN65" s="45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -11701,7 +11677,7 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -11749,13 +11725,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M66" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M66" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O66" s="38" t="inlineStr">
         <is>
@@ -11798,78 +11774,72 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X66" s="57" t="n">
+      <c r="X66" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA66" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD66" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG66" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI66" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK66" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL66" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="Y66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z66" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD66" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE66" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM66" s="44" t="n">
-        <v>3</v>
-      </c>
       <c r="AN66" s="45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -12237,7 +12207,7 @@
     <row r="69">
       <c r="A69" s="46" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="B69" s="47" t="inlineStr">
@@ -12247,7 +12217,7 @@
       </c>
       <c r="C69" s="47" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57392556500</t>
         </is>
       </c>
       <c r="D69" s="48" t="inlineStr">
@@ -12285,10 +12255,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K69" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="L69" s="48" t="inlineStr">
         <is>
@@ -12300,8 +12268,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N69" s="53" t="n">
-        <v>1</v>
+      <c r="N69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="48" t="inlineStr">
         <is>
@@ -12344,10 +12314,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X69" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="Y69" s="48" t="inlineStr">
         <is>
@@ -12359,8 +12327,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA69" s="58" t="n">
-        <v>1</v>
+      <c r="AA69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB69" s="48" t="inlineStr">
         <is>
@@ -12372,11 +12342,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD69" s="50" t="n">
-        <v>1</v>
+      <c r="AD69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE69" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF69" s="48" t="inlineStr">
         <is>
@@ -12408,16 +12380,16 @@
         <v>1</v>
       </c>
       <c r="AM69" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN69" s="45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>Armando Jose Mercado Vega</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -12427,13 +12399,11 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>57392556500</t>
-        </is>
-      </c>
-      <c r="D70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57824284000</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
@@ -12455,18 +12425,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>1</v>
+      <c r="I70" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L70" s="38" t="inlineStr">
         <is>
@@ -12488,11 +12456,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P70" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="55" t="n">
-        <v>1</v>
+      <c r="P70" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q70" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R70" s="39" t="inlineStr">
         <is>
@@ -12504,10 +12476,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T70" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T70" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="39" t="inlineStr">
         <is>
@@ -12519,13 +12489,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W70" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W70" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X70" s="57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y70" s="40" t="inlineStr">
         <is>
@@ -12557,16 +12525,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE70" s="42" t="n">
-        <v>4</v>
+      <c r="AE70" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF70" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG70" s="28" t="n">
-        <v>1</v>
+      <c r="AG70" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH70" s="43" t="inlineStr">
         <is>
@@ -12583,23 +12555,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK70" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL70" s="61" t="n">
-        <v>1</v>
+      <c r="AK70" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL70" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM70" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN70" s="45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="46" t="inlineStr">
         <is>
-          <t>Armando Jose Mercado Vega</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B71" s="47" t="inlineStr">
@@ -12609,16 +12585,16 @@
       </c>
       <c r="C71" s="47" t="inlineStr">
         <is>
-          <t>57824284000</t>
-        </is>
-      </c>
-      <c r="D71" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57204842254</t>
+        </is>
+      </c>
+      <c r="D71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F71" s="48" t="inlineStr">
         <is>
@@ -12686,8 +12662,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T71" s="58" t="n">
-        <v>1</v>
+      <c r="T71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U71" s="48" t="inlineStr">
         <is>
@@ -12699,21 +12677,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W71" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X71" s="51" t="n">
-        <v>1</v>
+      <c r="W71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X71" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y71" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z71" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="48" t="inlineStr">
         <is>
@@ -12730,15 +12710,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE71" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE71" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AF71" s="48" t="inlineStr">
         <is>
@@ -12785,7 +12761,7 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
@@ -12795,7 +12771,7 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>57204842254</t>
+          <t>58620428800</t>
         </is>
       </c>
       <c r="D72" s="35" t="inlineStr">
@@ -12803,8 +12779,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="8" t="n">
-        <v>1</v>
+      <c r="E72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
@@ -12821,8 +12799,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I72" s="36" t="n">
-        <v>1</v>
+      <c r="I72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J72" s="37" t="n">
         <v>1</v>
@@ -12842,25 +12822,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N72" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N72" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O72" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P72" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P72" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="R72" s="39" t="inlineStr">
         <is>
@@ -12892,10 +12866,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X72" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X72" s="57" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="40" t="inlineStr">
         <is>
@@ -12924,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="AE72" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF72" s="43" t="inlineStr">
         <is>
@@ -12965,13 +12937,13 @@
         <v>2</v>
       </c>
       <c r="AN72" s="45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="46" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="B73" s="47" t="inlineStr">
@@ -12981,7 +12953,7 @@
       </c>
       <c r="C73" s="47" t="inlineStr">
         <is>
-          <t>58620428800</t>
+          <t>59326410200</t>
         </is>
       </c>
       <c r="D73" s="48" t="inlineStr">
@@ -13014,8 +12986,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J73" s="51" t="n">
-        <v>1</v>
+      <c r="J73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K73" s="48" t="inlineStr">
         <is>
@@ -13032,52 +13006,58 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N73" s="53" t="n">
-        <v>1</v>
+      <c r="N73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="51" t="n">
+      <c r="P73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X73" s="51" t="n">
         <v>2</v>
-      </c>
-      <c r="R73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X73" s="51" t="n">
-        <v>4</v>
       </c>
       <c r="Y73" s="48" t="inlineStr">
         <is>
@@ -13144,16 +13124,16 @@
         </is>
       </c>
       <c r="AM73" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN73" s="45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>Rita Cecilia de la Hoz del Villar</t>
+          <t>Gabriel Roman Melendez</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -13163,7 +13143,7 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>59326410200</t>
+          <t>56006978600</t>
         </is>
       </c>
       <c r="D74" s="35" t="inlineStr">
@@ -13216,25 +13196,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N74" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N74" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O74" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P74" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q74" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P74" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R74" s="39" t="inlineStr">
         <is>
@@ -13266,16 +13240,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X74" s="57" t="n">
-        <v>2</v>
+      <c r="X74" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y74" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z74" s="23" t="n">
-        <v>1</v>
+      <c r="Z74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA74" s="40" t="inlineStr">
         <is>
@@ -13292,11 +13270,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD74" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="42" t="n">
-        <v>3</v>
+      <c r="AD74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF74" s="43" t="inlineStr">
         <is>
@@ -13337,7 +13319,7 @@
         <v>1</v>
       </c>
       <c r="AN74" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -13535,7 +13517,7 @@
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>Augusto Andres Alean Romero</t>
+          <t>Daniel Toro Gonzalez</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
@@ -13545,13 +13527,11 @@
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>58954857900</t>
-        </is>
-      </c>
-      <c r="D76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>56380539800</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
@@ -13573,15 +13553,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I76" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K76" s="38" t="inlineStr">
         <is>
@@ -13618,8 +13594,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R76" s="17" t="n">
-        <v>1</v>
+      <c r="R76" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S76" s="39" t="inlineStr">
         <is>
@@ -13641,11 +13619,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W76" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" s="57" t="n">
-        <v>1</v>
+      <c r="W76" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X76" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y76" s="40" t="inlineStr">
         <is>
@@ -13727,7 +13709,7 @@
     <row r="77">
       <c r="A77" s="46" t="inlineStr">
         <is>
-          <t>Gabriel Roman Melendez</t>
+          <t>Alba Zulay Cardenas Escobar</t>
         </is>
       </c>
       <c r="B77" s="47" t="inlineStr">
@@ -13737,7 +13719,7 @@
       </c>
       <c r="C77" s="47" t="inlineStr">
         <is>
-          <t>56006978600</t>
+          <t>57930948900</t>
         </is>
       </c>
       <c r="D77" s="48" t="inlineStr">
@@ -13770,10 +13752,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J77" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="K77" s="48" t="inlineStr">
         <is>
@@ -13790,19 +13770,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N77" s="53" t="n">
-        <v>1</v>
+      <c r="N77" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P77" s="50" t="n">
-        <v>1</v>
+      <c r="P77" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q77" s="51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R77" s="48" t="inlineStr">
         <is>
@@ -13834,10 +13818,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X77" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X77" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="Y77" s="48" t="inlineStr">
         <is>
@@ -13869,10 +13851,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE77" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE77" s="51" t="n">
+        <v>6</v>
       </c>
       <c r="AF77" s="48" t="inlineStr">
         <is>
@@ -13910,16 +13890,16 @@
         </is>
       </c>
       <c r="AM77" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN77" s="45" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>Daniel Toro Gonzalez</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
@@ -13929,11 +13909,13 @@
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>56380539800</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>1</v>
+          <t>59326202000</t>
+        </is>
+      </c>
+      <c r="D78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E78" s="35" t="inlineStr">
         <is>
@@ -13955,11 +13937,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="37" t="n">
-        <v>1</v>
+      <c r="I78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K78" s="38" t="inlineStr">
         <is>
@@ -14026,10 +14012,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X78" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X78" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="Y78" s="40" t="inlineStr">
         <is>
@@ -14061,10 +14045,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE78" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE78" s="42" t="n">
+        <v>3</v>
       </c>
       <c r="AF78" s="43" t="inlineStr">
         <is>
@@ -14102,16 +14084,16 @@
         </is>
       </c>
       <c r="AM78" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN78" s="45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="46" t="inlineStr">
         <is>
-          <t>Alba Zulay Cardenas Escobar</t>
+          <t>Juan Camilo Medellin Rojas</t>
         </is>
       </c>
       <c r="B79" s="47" t="inlineStr">
@@ -14121,7 +14103,7 @@
       </c>
       <c r="C79" s="47" t="inlineStr">
         <is>
-          <t>57930948900</t>
+          <t>60150905000</t>
         </is>
       </c>
       <c r="D79" s="48" t="inlineStr">
@@ -14154,8 +14136,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J79" s="51" t="n">
-        <v>4</v>
+      <c r="J79" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K79" s="48" t="inlineStr">
         <is>
@@ -14187,8 +14171,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q79" s="51" t="n">
-        <v>3</v>
+      <c r="Q79" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R79" s="48" t="inlineStr">
         <is>
@@ -14220,8 +14206,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X79" s="51" t="n">
-        <v>4</v>
+      <c r="X79" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y79" s="48" t="inlineStr">
         <is>
@@ -14254,7 +14242,7 @@
         </is>
       </c>
       <c r="AE79" s="51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF79" s="48" t="inlineStr">
         <is>
@@ -14295,13 +14283,13 @@
         <v>0</v>
       </c>
       <c r="AN79" s="45" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo</t>
+          <t>Martha Patricia Castro Porto</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -14311,7 +14299,7 @@
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
-          <t>59326202000</t>
+          <t>58928816700</t>
         </is>
       </c>
       <c r="D80" s="35" t="inlineStr">
@@ -14379,10 +14367,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q80" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q80" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R80" s="39" t="inlineStr">
         <is>
@@ -14415,7 +14401,7 @@
         </is>
       </c>
       <c r="X80" s="57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y80" s="40" t="inlineStr">
         <is>
@@ -14447,8 +14433,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE80" s="42" t="n">
-        <v>3</v>
+      <c r="AE80" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF80" s="43" t="inlineStr">
         <is>
@@ -14489,230 +14477,37 @@
         <v>0</v>
       </c>
       <c r="AN80" s="45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="46" t="inlineStr">
-        <is>
-          <t>Juan Camilo Medellin Rojas</t>
-        </is>
-      </c>
-      <c r="B81" s="47" t="inlineStr">
-        <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
-        </is>
-      </c>
-      <c r="C81" s="47" t="inlineStr">
-        <is>
-          <t>60150905000</t>
-        </is>
-      </c>
-      <c r="D81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE81" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL81" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM81" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN81" s="45" t="n">
-        <v>1</v>
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>Martha Patricia Castro Porto</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C82" s="34" t="inlineStr">
         <is>
-          <t>58928816700</t>
-        </is>
-      </c>
-      <c r="D82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57191333650</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="F82" s="35" t="inlineStr">
         <is>
@@ -14729,58 +14524,42 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I82" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>4</v>
       </c>
       <c r="L82" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O82" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P82" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P82" s="54" t="n">
+        <v>6</v>
       </c>
       <c r="Q82" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="R82" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S82" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="T82" s="39" t="inlineStr">
         <is>
@@ -14797,23 +14576,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W82" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W82" s="56" t="n">
+        <v>5</v>
       </c>
       <c r="X82" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="Y82" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z82" s="23" t="n">
+        <v>3</v>
       </c>
       <c r="AA82" s="40" t="inlineStr">
         <is>
@@ -14830,30 +14603,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD82" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE82" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF82" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG82" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH82" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="AI82" s="43" t="inlineStr">
         <is>
@@ -14865,34 +14628,177 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL82" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK82" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL82" s="59" t="n">
+        <v>7</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
-        </is>
+      <c r="A83" s="46" t="inlineStr">
+        <is>
+          <t>Miguel Efren Garces Prettel</t>
+        </is>
+      </c>
+      <c r="B83" s="47" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="C83" s="47" t="inlineStr">
+        <is>
+          <t>57193012270</t>
+        </is>
+      </c>
+      <c r="D83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="S83" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U83" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W83" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="X83" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD83" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE83" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF83" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH83" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ83" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK83" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL83" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM83" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN83" s="45" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -14902,14 +14808,16 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>57191333650</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="8" t="n">
-        <v>2</v>
+      <c r="E84" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F84" s="35" t="inlineStr">
         <is>
@@ -14927,41 +14835,45 @@
         </is>
       </c>
       <c r="I84" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J84" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="K84" s="12" t="n">
+      <c r="L84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="L84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P84" s="54" t="n">
-        <v>6</v>
-      </c>
       <c r="Q84" s="55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R84" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="S84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="T84" s="39" t="inlineStr">
         <is>
@@ -14979,16 +14891,18 @@
         </is>
       </c>
       <c r="W84" s="56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X84" s="57" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y84" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z84" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="Z84" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA84" s="40" t="inlineStr">
         <is>
@@ -15006,19 +14920,23 @@
         </is>
       </c>
       <c r="AD84" s="41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE84" s="42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF84" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG84" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH84" s="29" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AG84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI84" s="43" t="inlineStr">
         <is>
@@ -15031,13 +14949,13 @@
         </is>
       </c>
       <c r="AK84" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL84" s="61" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="AL84" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM84" s="44" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AN84" s="45" t="n">
         <v>31</v>
@@ -15046,7 +14964,7 @@
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
@@ -15056,19 +14974,21 @@
       </c>
       <c r="C85" s="47" t="inlineStr">
         <is>
-          <t>57193012270</t>
-        </is>
-      </c>
-      <c r="D85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="58" t="n">
-        <v>1</v>
+          <t>57202285682</t>
+        </is>
+      </c>
+      <c r="D85" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G85" s="48" t="inlineStr">
         <is>
@@ -15081,126 +15001,138 @@
         </is>
       </c>
       <c r="I85" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P85" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="J85" s="51" t="n">
+      <c r="Q85" s="51" t="n">
+        <v>12</v>
+      </c>
+      <c r="R85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X85" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y85" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD85" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K85" s="49" t="n">
+      <c r="AE85" s="51" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF85" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK85" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL85" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="L85" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N85" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P85" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q85" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="R85" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="S85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U85" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W85" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="X85" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD85" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE85" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF85" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH85" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK85" s="50" t="n">
+      <c r="AM85" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="AL85" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM85" s="44" t="n">
-        <v>19</v>
-      </c>
       <c r="AN85" s="45" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -15210,11 +15142,13 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>57156565000</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>1</v>
+          <t>26325154200</t>
+        </is>
+      </c>
+      <c r="D86" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E86" s="35" t="inlineStr">
         <is>
@@ -15236,22 +15170,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="36" t="n">
-        <v>1</v>
+      <c r="I86" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J86" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M86" s="14" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N86" s="38" t="inlineStr">
         <is>
@@ -15264,13 +15200,15 @@
         </is>
       </c>
       <c r="P86" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q86" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="R86" s="17" t="n">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R86" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S86" s="39" t="inlineStr">
         <is>
@@ -15292,8 +15230,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W86" s="56" t="n">
-        <v>1</v>
+      <c r="W86" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X86" s="57" t="n">
         <v>15</v>
@@ -15301,10 +15241,8 @@
       <c r="Y86" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z86" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="40" t="inlineStr">
         <is>
@@ -15322,57 +15260,51 @@
         </is>
       </c>
       <c r="AD86" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE86" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF86" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ86" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK86" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL86" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="AF86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AM86" s="44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN86" s="45" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="46" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="B87" s="47" t="inlineStr">
@@ -15382,16 +15314,16 @@
       </c>
       <c r="C87" s="47" t="inlineStr">
         <is>
-          <t>57202285682</t>
-        </is>
-      </c>
-      <c r="D87" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57216868622</t>
+        </is>
+      </c>
+      <c r="D87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F87" s="48" t="inlineStr">
         <is>
@@ -15412,74 +15344,80 @@
         <v>1</v>
       </c>
       <c r="J87" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z87" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P87" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q87" s="51" t="n">
-        <v>12</v>
-      </c>
-      <c r="R87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X87" s="51" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y87" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z87" s="52" t="n">
-        <v>1</v>
-      </c>
       <c r="AA87" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -15496,13 +15434,15 @@
         </is>
       </c>
       <c r="AD87" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE87" s="51" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF87" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AF87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG87" s="48" t="inlineStr">
         <is>
@@ -15524,23 +15464,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK87" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL87" s="51" t="n">
-        <v>2</v>
+      <c r="AK87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM87" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN87" s="45" t="n">
         <v>6</v>
-      </c>
-      <c r="AN87" s="45" t="n">
-        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -15550,7 +15494,7 @@
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>26325154200</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D88" s="35" t="inlineStr">
@@ -15583,95 +15527,107 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J88" s="37" t="n">
+      <c r="J88" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X88" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y88" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z88" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD88" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P88" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q88" s="55" t="n">
-        <v>14</v>
-      </c>
-      <c r="R88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W88" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X88" s="57" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y88" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z88" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC88" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD88" s="41" t="n">
-        <v>2</v>
-      </c>
       <c r="AE88" s="42" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="AF88" s="27" t="n">
         <v>1</v>
@@ -15699,20 +15655,20 @@
       <c r="AK88" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="AL88" s="61" t="n">
+      <c r="AL88" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM88" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="AM88" s="44" t="n">
-        <v>5</v>
-      </c>
       <c r="AN88" s="45" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="46" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="B89" s="47" t="inlineStr">
@@ -15722,7 +15678,7 @@
       </c>
       <c r="C89" s="47" t="inlineStr">
         <is>
-          <t>57216868622</t>
+          <t>57206773929</t>
         </is>
       </c>
       <c r="D89" s="48" t="inlineStr">
@@ -15730,8 +15686,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E89" s="52" t="n">
-        <v>1</v>
+      <c r="E89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F89" s="48" t="inlineStr">
         <is>
@@ -15748,40 +15706,42 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I89" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="51" t="n">
+      <c r="I89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O89" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P89" s="50" t="n">
-        <v>1</v>
-      </c>
       <c r="Q89" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" s="48" t="inlineStr">
         <is>
@@ -15798,25 +15758,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U89" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V89" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X89" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y89" s="48" t="inlineStr">
         <is>
@@ -15824,7 +15778,7 @@
         </is>
       </c>
       <c r="Z89" s="52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA89" s="48" t="inlineStr">
         <is>
@@ -15842,10 +15796,10 @@
         </is>
       </c>
       <c r="AD89" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE89" s="51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF89" s="48" t="inlineStr">
         <is>
@@ -15883,16 +15837,16 @@
         </is>
       </c>
       <c r="AM89" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="45" t="n">
         <v>5</v>
-      </c>
-      <c r="AN89" s="45" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Maria Fernanda Medina Reyes</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -15902,7 +15856,7 @@
       </c>
       <c r="C90" s="34" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>57221229836</t>
         </is>
       </c>
       <c r="D90" s="35" t="inlineStr">
@@ -15910,10 +15864,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E90" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E90" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F90" s="35" t="inlineStr">
         <is>
@@ -15930,15 +15882,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I90" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J90" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I90" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K90" s="38" t="inlineStr">
         <is>
@@ -15985,10 +15933,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T90" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T90" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="39" t="inlineStr">
         <is>
@@ -16000,18 +15946,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W90" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X90" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y90" s="22" t="n">
-        <v>2</v>
+      <c r="W90" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X90" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z90" s="23" t="n">
         <v>1</v>
@@ -16032,13 +15976,15 @@
         </is>
       </c>
       <c r="AD90" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE90" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="AE90" s="42" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF90" s="27" t="n">
-        <v>1</v>
+      <c r="AF90" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG90" s="43" t="inlineStr">
         <is>
@@ -16060,23 +16006,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK90" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL90" s="61" t="n">
-        <v>1</v>
+      <c r="AK90" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL90" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM90" s="44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN90" s="45" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="46" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>Humberto Manuel Marbello Peña</t>
         </is>
       </c>
       <c r="B91" s="47" t="inlineStr">
@@ -16086,7 +16036,7 @@
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t>57206773929</t>
+          <t>59325343900</t>
         </is>
       </c>
       <c r="D91" s="48" t="inlineStr">
@@ -16124,8 +16074,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="49" t="n">
-        <v>1</v>
+      <c r="K91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L91" s="48" t="inlineStr">
         <is>
@@ -16142,51 +16094,63 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O91" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" s="50" t="n">
+      <c r="O91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X91" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="Q91" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U91" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W91" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X91" s="51" t="n">
-        <v>1</v>
-      </c>
       <c r="Y91" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z91" s="52" t="n">
-        <v>1</v>
+      <c r="Z91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA91" s="48" t="inlineStr">
         <is>
@@ -16203,21 +16167,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD91" s="50" t="n">
-        <v>1</v>
+      <c r="AD91" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE91" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF91" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG91" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH91" s="48" t="inlineStr">
         <is>
@@ -16234,27 +16198,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL91" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK91" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL91" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM91" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN91" s="45" t="n">
         <v>4</v>
-      </c>
-      <c r="AN91" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes</t>
+          <t>Misorly del Carmen Soto Acevedo</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -16264,7 +16224,7 @@
       </c>
       <c r="C92" s="34" t="inlineStr">
         <is>
-          <t>57221229836</t>
+          <t>58523088300</t>
         </is>
       </c>
       <c r="D92" s="35" t="inlineStr">
@@ -16272,8 +16232,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E92" s="8" t="n">
-        <v>1</v>
+      <c r="E92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F92" s="35" t="inlineStr">
         <is>
@@ -16290,11 +16252,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I92" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="37" t="n">
-        <v>1</v>
+      <c r="I92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K92" s="38" t="inlineStr">
         <is>
@@ -16306,10 +16272,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M92" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M92" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="N92" s="38" t="inlineStr">
         <is>
@@ -16321,15 +16285,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P92" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q92" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P92" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R92" s="39" t="inlineStr">
         <is>
@@ -16341,8 +16301,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T92" s="19" t="n">
-        <v>1</v>
+      <c r="T92" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U92" s="39" t="inlineStr">
         <is>
@@ -16354,19 +16316,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W92" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X92" s="57" t="n">
-        <v>1</v>
+      <c r="W92" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X92" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y92" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z92" s="23" t="n">
-        <v>1</v>
+      <c r="Z92" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA92" s="40" t="inlineStr">
         <is>
@@ -16383,11 +16351,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD92" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE92" s="42" t="n">
-        <v>3</v>
+      <c r="AD92" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE92" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF92" s="43" t="inlineStr">
         <is>
@@ -16425,16 +16397,16 @@
         </is>
       </c>
       <c r="AM92" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN92" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="46" t="inlineStr">
         <is>
-          <t>Misorly del Carmen Soto Acevedo</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="B93" s="47" t="inlineStr">
@@ -16444,7 +16416,7 @@
       </c>
       <c r="C93" s="47" t="inlineStr">
         <is>
-          <t>58523088300</t>
+          <t>57220927199</t>
         </is>
       </c>
       <c r="D93" s="48" t="inlineStr">
@@ -16477,10 +16449,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J93" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K93" s="48" t="inlineStr">
         <is>
@@ -16492,8 +16462,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M93" s="58" t="n">
-        <v>1</v>
+      <c r="M93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N93" s="48" t="inlineStr">
         <is>
@@ -16505,11 +16477,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P93" s="50" t="n">
-        <v>1</v>
+      <c r="P93" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q93" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R93" s="48" t="inlineStr">
         <is>
@@ -16541,10 +16515,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X93" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="Y93" s="48" t="inlineStr">
         <is>
@@ -16576,10 +16548,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE93" s="51" t="n">
+        <v>22</v>
       </c>
       <c r="AF93" s="48" t="inlineStr">
         <is>
@@ -16611,22 +16581,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL93" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AM93" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN93" s="45" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña</t>
+          <t>Julio Antonio Gomez Mora</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -16636,7 +16604,7 @@
       </c>
       <c r="C94" s="34" t="inlineStr">
         <is>
-          <t>59325343900</t>
+          <t>60514611700</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
@@ -16739,8 +16707,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X94" s="57" t="n">
-        <v>2</v>
+      <c r="X94" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y94" s="40" t="inlineStr">
         <is>
@@ -16780,8 +16750,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG94" s="28" t="n">
-        <v>1</v>
+      <c r="AG94" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH94" s="43" t="inlineStr">
         <is>
@@ -16798,23 +16770,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK94" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL94" s="61" t="n">
-        <v>1</v>
+      <c r="AK94" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL94" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM94" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN94" s="45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="46" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Yuranis Henriquez Nuñez</t>
         </is>
       </c>
       <c r="B95" s="47" t="inlineStr">
@@ -16824,7 +16800,7 @@
       </c>
       <c r="C95" s="47" t="inlineStr">
         <is>
-          <t>57220927199</t>
+          <t>57982471000</t>
         </is>
       </c>
       <c r="D95" s="48" t="inlineStr">
@@ -16891,7 +16867,7 @@
         </is>
       </c>
       <c r="Q95" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" s="48" t="inlineStr">
         <is>
@@ -16923,8 +16899,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X95" s="51" t="n">
-        <v>2</v>
+      <c r="X95" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y95" s="48" t="inlineStr">
         <is>
@@ -16957,7 +16935,7 @@
         </is>
       </c>
       <c r="AE95" s="51" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AF95" s="48" t="inlineStr">
         <is>
@@ -16989,20 +16967,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL95" s="51" t="n">
-        <v>2</v>
+      <c r="AL95" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM95" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AN95" s="45" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>Julio Antonio Gomez Mora</t>
+          <t>Isaac Zuñiga Silgado</t>
         </is>
       </c>
       <c r="B96" s="34" t="inlineStr">
@@ -17012,7 +16992,7 @@
       </c>
       <c r="C96" s="34" t="inlineStr">
         <is>
-          <t>60514611700</t>
+          <t>60157655200</t>
         </is>
       </c>
       <c r="D96" s="35" t="inlineStr">
@@ -17198,7 +17178,7 @@
     <row r="97">
       <c r="A97" s="46" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez</t>
+          <t>Marelbi del Carmen Olmos Perez</t>
         </is>
       </c>
       <c r="B97" s="47" t="inlineStr">
@@ -17208,7 +17188,7 @@
       </c>
       <c r="C97" s="47" t="inlineStr">
         <is>
-          <t>57982471000</t>
+          <t>58868256900</t>
         </is>
       </c>
       <c r="D97" s="48" t="inlineStr">
@@ -17241,8 +17221,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J97" s="51" t="n">
-        <v>1</v>
+      <c r="J97" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K97" s="48" t="inlineStr">
         <is>
@@ -17342,8 +17324,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE97" s="51" t="n">
-        <v>3</v>
+      <c r="AE97" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF97" s="48" t="inlineStr">
         <is>
@@ -17384,398 +17368,6 @@
         <v>0</v>
       </c>
       <c r="AN97" s="45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="33" t="inlineStr">
-        <is>
-          <t>Isaac Zuñiga Silgado</t>
-        </is>
-      </c>
-      <c r="B98" s="34" t="inlineStr">
-        <is>
-          <t>Escuela de Transformación Digital</t>
-        </is>
-      </c>
-      <c r="C98" s="34" t="inlineStr">
-        <is>
-          <t>60157655200</t>
-        </is>
-      </c>
-      <c r="D98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J98" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q98" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X98" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD98" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE98" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL98" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM98" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN98" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="46" t="inlineStr">
-        <is>
-          <t>Marelbi del Carmen Olmos Perez</t>
-        </is>
-      </c>
-      <c r="B99" s="47" t="inlineStr">
-        <is>
-          <t>Escuela de Transformación Digital</t>
-        </is>
-      </c>
-      <c r="C99" s="47" t="inlineStr">
-        <is>
-          <t>58868256900</t>
-        </is>
-      </c>
-      <c r="D99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q99" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL99" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AM99" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17784,16 +17376,16 @@
     <mergeCell ref="Y1:AE1"/>
     <mergeCell ref="A3:AN3"/>
     <mergeCell ref="A6:AN6"/>
-    <mergeCell ref="A83:AN83"/>
     <mergeCell ref="AM1:AN1"/>
     <mergeCell ref="A21:AN21"/>
     <mergeCell ref="R1:X1"/>
-    <mergeCell ref="A59:AN59"/>
+    <mergeCell ref="A81:AN81"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A23:AN23"/>
     <mergeCell ref="AF1:AL1"/>
     <mergeCell ref="D1:J1"/>
+    <mergeCell ref="A58:AN58"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -7020,7 +7020,7 @@
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>57215550013</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
@@ -7133,11 +7133,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X40" s="57" t="n">
-        <v>1</v>
+      <c r="X40" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y40" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="40" t="inlineStr">
         <is>
@@ -7160,20 +7162,18 @@
         </is>
       </c>
       <c r="AD40" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE40" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF40" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG40" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG40" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH40" s="43" t="inlineStr">
         <is>
@@ -7190,27 +7190,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK40" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL40" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK40" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM40" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN40" s="45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="B41" s="47" t="inlineStr">
@@ -7220,7 +7216,7 @@
       </c>
       <c r="C41" s="47" t="inlineStr">
         <is>
-          <t>58803522300</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
@@ -7288,11 +7284,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q41" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="49" t="n">
-        <v>1</v>
+      <c r="Q41" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R41" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S41" s="48" t="inlineStr">
         <is>
@@ -7314,17 +7314,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W41" s="50" t="n">
-        <v>1</v>
+      <c r="W41" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X41" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="Y41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Z41" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -7345,13 +7345,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD41" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AE41" s="51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF41" s="48" t="inlineStr">
         <is>
@@ -7389,16 +7387,16 @@
         </is>
       </c>
       <c r="AM41" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN41" s="45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Angela Patricia Barreto Maya</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
@@ -7408,7 +7406,7 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>59269721500</t>
+          <t>58803522300</t>
         </is>
       </c>
       <c r="D42" s="35" t="inlineStr">
@@ -7476,10 +7474,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q42" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q42" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R42" s="17" t="n">
         <v>1</v>
@@ -7508,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="X42" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y42" s="40" t="inlineStr">
         <is>
@@ -7540,10 +7536,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE42" s="42" t="n">
+        <v>4</v>
       </c>
       <c r="AF42" s="43" t="inlineStr">
         <is>
@@ -7584,13 +7578,13 @@
         <v>1</v>
       </c>
       <c r="AN42" s="45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="46" t="inlineStr">
         <is>
-          <t>Oscar Acevedo Patiño</t>
+          <t>Angela Patricia Barreto Maya</t>
         </is>
       </c>
       <c r="B43" s="47" t="inlineStr">
@@ -7600,7 +7594,7 @@
       </c>
       <c r="C43" s="47" t="inlineStr">
         <is>
-          <t>57197327858</t>
+          <t>59269721500</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
@@ -7633,8 +7627,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J43" s="51" t="n">
-        <v>2</v>
+      <c r="J43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K43" s="48" t="inlineStr">
         <is>
@@ -7671,10 +7667,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R43" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S43" s="48" t="inlineStr">
         <is>
@@ -7696,21 +7690,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W43" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X43" s="51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z43" s="52" t="n">
-        <v>1</v>
+      <c r="Z43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA43" s="48" t="inlineStr">
         <is>
@@ -7727,11 +7721,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD43" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="51" t="n">
-        <v>3</v>
+      <c r="AD43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF43" s="48" t="inlineStr">
         <is>
@@ -7772,13 +7770,13 @@
         <v>1</v>
       </c>
       <c r="AN43" s="45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -7788,7 +7786,7 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>7005142049</t>
+          <t>57197327858</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -7822,7 +7820,7 @@
         </is>
       </c>
       <c r="J44" s="37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
@@ -7854,8 +7852,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q44" s="55" t="n">
-        <v>9</v>
+      <c r="Q44" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R44" s="39" t="inlineStr">
         <is>
@@ -7888,15 +7888,15 @@
         </is>
       </c>
       <c r="X44" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="Y44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z44" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="40" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>1</v>
       </c>
       <c r="AE44" s="42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="43" t="inlineStr">
         <is>
@@ -7949,20 +7949,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL44" s="59" t="n">
-        <v>1</v>
+      <c r="AL44" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM44" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN44" s="45" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="B45" s="47" t="inlineStr">
@@ -7972,7 +7974,7 @@
       </c>
       <c r="C45" s="47" t="inlineStr">
         <is>
-          <t>57205400052</t>
+          <t>7005142049</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
@@ -8005,10 +8007,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J45" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="K45" s="48" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="Q45" s="51" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R45" s="48" t="inlineStr">
         <is>
@@ -8074,15 +8074,15 @@
         </is>
       </c>
       <c r="X45" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z45" s="52" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="Y45" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA45" s="48" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>1</v>
       </c>
       <c r="AE45" s="51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF45" s="48" t="inlineStr">
         <is>
@@ -8135,22 +8135,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL45" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM45" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN45" s="45" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>Lien Neil Tejeda López</t>
+          <t>Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
@@ -8160,7 +8158,7 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>60026192200</t>
+          <t>57205400052</t>
         </is>
       </c>
       <c r="D46" s="35" t="inlineStr">
@@ -8228,10 +8226,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q46" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q46" s="55" t="n">
+        <v>4</v>
       </c>
       <c r="R46" s="39" t="inlineStr">
         <is>
@@ -8263,23 +8259,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X46" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X46" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="Y46" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z46" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA46" s="24" t="n">
-        <v>1</v>
+      <c r="Z46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB46" s="40" t="inlineStr">
         <is>
@@ -8295,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="AE46" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF46" s="43" t="inlineStr">
         <is>
@@ -8336,13 +8330,13 @@
         <v>1</v>
       </c>
       <c r="AN46" s="45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="46" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Lien Neil Tejeda López</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -8352,7 +8346,7 @@
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>57197028938</t>
+          <t>60026192200</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
@@ -8460,18 +8454,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y47" s="49" t="n">
-        <v>1</v>
+      <c r="Y47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z47" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA47" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AB47" s="48" t="inlineStr">
         <is>
@@ -8534,7 +8528,7 @@
     <row r="48">
       <c r="A48" s="33" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
@@ -8544,7 +8538,7 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>57215550013</t>
+          <t>57197028938</t>
         </is>
       </c>
       <c r="D48" s="35" t="inlineStr">
@@ -14764,7 +14758,7 @@
         <v>2</v>
       </c>
       <c r="AF83" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG83" s="52" t="n">
         <v>1</v>
@@ -14783,16 +14777,16 @@
         </is>
       </c>
       <c r="AK83" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL83" s="51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM83" s="44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN83" s="45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84">
@@ -14964,7 +14958,7 @@
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
@@ -14974,11 +14968,13 @@
       </c>
       <c r="C85" s="47" t="inlineStr">
         <is>
-          <t>57202285682</t>
-        </is>
-      </c>
-      <c r="D85" s="49" t="n">
-        <v>1</v>
+          <t>26325154200</t>
+        </is>
+      </c>
+      <c r="D85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E85" s="48" t="inlineStr">
         <is>
@@ -15000,8 +14996,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="50" t="n">
-        <v>1</v>
+      <c r="I85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J85" s="51" t="n">
         <v>3</v>
@@ -15031,7 +15029,7 @@
         <v>2</v>
       </c>
       <c r="Q85" s="51" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R85" s="48" t="inlineStr">
         <is>
@@ -15091,15 +15089,13 @@
         <v>2</v>
       </c>
       <c r="AE85" s="51" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AF85" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="AG85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG85" s="52" t="n">
+        <v>2</v>
       </c>
       <c r="AH85" s="48" t="inlineStr">
         <is>
@@ -15117,22 +15113,22 @@
         </is>
       </c>
       <c r="AK85" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL85" s="51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM85" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN85" s="45" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -15142,13 +15138,11 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>26325154200</t>
-        </is>
-      </c>
-      <c r="D86" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57202285682</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E86" s="35" t="inlineStr">
         <is>
@@ -15170,10 +15164,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I86" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="J86" s="37" t="n">
         <v>3</v>
@@ -15203,7 +15195,7 @@
         <v>2</v>
       </c>
       <c r="Q86" s="55" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R86" s="39" t="inlineStr">
         <is>
@@ -15263,7 +15255,7 @@
         <v>2</v>
       </c>
       <c r="AE86" s="42" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AF86" s="27" t="n">
         <v>1</v>
@@ -15292,13 +15284,13 @@
         <v>1</v>
       </c>
       <c r="AL86" s="59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM86" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN86" s="45" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87">
@@ -15630,7 +15622,7 @@
         <v>19</v>
       </c>
       <c r="AF88" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG88" s="43" t="inlineStr">
         <is>
@@ -15653,16 +15645,16 @@
         </is>
       </c>
       <c r="AK88" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL88" s="59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM88" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN88" s="45" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -3009,7 +3009,7 @@
         <v>2</v>
       </c>
       <c r="AE15" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF15" s="48" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>2</v>
       </c>
       <c r="AN15" s="45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -14607,7 +14607,7 @@
         <v>4</v>
       </c>
       <c r="AG82" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH82" s="29" t="n">
         <v>2</v>
@@ -14623,16 +14623,16 @@
         </is>
       </c>
       <c r="AK82" s="45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL82" s="59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -14792,7 +14792,7 @@
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>57202285682</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
@@ -14832,18 +14832,18 @@
         <v>1</v>
       </c>
       <c r="J84" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="14" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N84" s="38" t="inlineStr">
         <is>
@@ -14856,13 +14856,15 @@
         </is>
       </c>
       <c r="P84" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="R84" s="17" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="R84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S84" s="39" t="inlineStr">
         <is>
@@ -14884,8 +14886,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W84" s="56" t="n">
-        <v>1</v>
+      <c r="W84" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X84" s="57" t="n">
         <v>15</v>
@@ -14893,10 +14897,8 @@
       <c r="Y84" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z84" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="40" t="inlineStr">
         <is>
@@ -14914,51 +14916,49 @@
         </is>
       </c>
       <c r="AD84" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE84" s="42" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF84" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG84" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK84" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL84" s="59" t="n">
         <v>4</v>
-      </c>
-      <c r="AF84" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK84" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL84" s="59" t="n">
-        <v>1</v>
       </c>
       <c r="AM84" s="44" t="n">
         <v>8</v>
       </c>
       <c r="AN84" s="45" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
@@ -14968,13 +14968,11 @@
       </c>
       <c r="C85" s="47" t="inlineStr">
         <is>
-          <t>26325154200</t>
-        </is>
-      </c>
-      <c r="D85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57156565000</t>
+        </is>
+      </c>
+      <c r="D85" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E85" s="48" t="inlineStr">
         <is>
@@ -14996,24 +14994,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I85" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M85" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="N85" s="48" t="inlineStr">
         <is>
@@ -15026,15 +15022,13 @@
         </is>
       </c>
       <c r="P85" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q85" s="51" t="n">
-        <v>14</v>
-      </c>
-      <c r="R85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="R85" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S85" s="48" t="inlineStr">
         <is>
@@ -15056,10 +15050,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W85" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W85" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X85" s="51" t="n">
         <v>15</v>
@@ -15067,8 +15059,10 @@
       <c r="Y85" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="Z85" s="52" t="n">
-        <v>1</v>
+      <c r="Z85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA85" s="48" t="inlineStr">
         <is>
@@ -15086,16 +15080,18 @@
         </is>
       </c>
       <c r="AD85" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE85" s="51" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="AF85" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="AG85" s="52" t="n">
-        <v>2</v>
+      <c r="AG85" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH85" s="48" t="inlineStr">
         <is>
@@ -15113,22 +15109,22 @@
         </is>
       </c>
       <c r="AK85" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL85" s="51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AM85" s="44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN85" s="45" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -15138,11 +15134,13 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>57202285682</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>1</v>
+          <t>26325154200</t>
+        </is>
+      </c>
+      <c r="D86" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E86" s="35" t="inlineStr">
         <is>
@@ -15164,8 +15162,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="36" t="n">
-        <v>1</v>
+      <c r="I86" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J86" s="37" t="n">
         <v>3</v>
@@ -15195,7 +15195,7 @@
         <v>2</v>
       </c>
       <c r="Q86" s="55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R86" s="39" t="inlineStr">
         <is>
@@ -15255,15 +15255,13 @@
         <v>2</v>
       </c>
       <c r="AE86" s="42" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AF86" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="AG86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG86" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="AH86" s="43" t="inlineStr">
         <is>
@@ -15281,22 +15279,22 @@
         </is>
       </c>
       <c r="AK86" s="45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL86" s="59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM86" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN86" s="45" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="46" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B87" s="47" t="inlineStr">
@@ -15306,7 +15304,7 @@
       </c>
       <c r="C87" s="47" t="inlineStr">
         <is>
-          <t>57216868622</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D87" s="48" t="inlineStr">
@@ -15314,8 +15312,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="52" t="n">
-        <v>1</v>
+      <c r="E87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F87" s="48" t="inlineStr">
         <is>
@@ -15332,83 +15332,91 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="51" t="n">
+      <c r="I87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y87" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="K87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M87" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P87" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Z87" s="52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA87" s="48" t="inlineStr">
         <is>
@@ -15429,54 +15437,46 @@
         <v>3</v>
       </c>
       <c r="AE87" s="51" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF87" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG87" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK87" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="AF87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL87" s="51" t="n">
+        <v>5</v>
       </c>
       <c r="AM87" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN87" s="45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>57216868622</t>
         </is>
       </c>
       <c r="D88" s="35" t="inlineStr">
@@ -15494,10 +15494,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E88" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F88" s="35" t="inlineStr">
         <is>
@@ -15514,15 +15512,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I88" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="37" t="n">
+        <v>2</v>
       </c>
       <c r="K88" s="38" t="inlineStr">
         <is>
@@ -15534,10 +15528,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M88" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="N88" s="38" t="inlineStr">
         <is>
@@ -15549,15 +15541,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q88" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P88" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R88" s="39" t="inlineStr">
         <is>
@@ -15594,11 +15582,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y88" s="22" t="n">
-        <v>2</v>
+      <c r="Y88" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z88" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA88" s="40" t="inlineStr">
         <is>
@@ -15619,10 +15609,12 @@
         <v>3</v>
       </c>
       <c r="AE88" s="42" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF88" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="AF88" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG88" s="43" t="inlineStr">
         <is>
@@ -15644,17 +15636,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK88" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL88" s="59" t="n">
-        <v>3</v>
+      <c r="AK88" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL88" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM88" s="44" t="n">
         <v>5</v>
       </c>
       <c r="AN88" s="45" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -7020,7 +7020,7 @@
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>57215550013</t>
+          <t>57197028938</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
@@ -7167,13 +7167,13 @@
       <c r="AE40" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="AF40" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG40" s="28" t="n">
-        <v>1</v>
+      <c r="AF40" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH40" s="43" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="B41" s="47" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="C41" s="47" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>57215550013</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
@@ -7319,11 +7319,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X41" s="51" t="n">
-        <v>1</v>
+      <c r="X41" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y41" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="48" t="inlineStr">
         <is>
@@ -7346,20 +7348,18 @@
         </is>
       </c>
       <c r="AD41" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE41" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF41" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG41" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH41" s="48" t="inlineStr">
         <is>
@@ -7376,27 +7376,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK41" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM41" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN41" s="45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
@@ -7406,7 +7402,7 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>58803522300</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="D42" s="35" t="inlineStr">
@@ -7474,11 +7470,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q42" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="17" t="n">
-        <v>1</v>
+      <c r="Q42" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R42" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S42" s="39" t="inlineStr">
         <is>
@@ -7500,17 +7500,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W42" s="56" t="n">
-        <v>1</v>
+      <c r="W42" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X42" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="Y42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Z42" s="40" t="inlineStr">
         <is>
           <t>—</t>
@@ -7531,13 +7531,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD42" s="41" t="n">
+        <v>2</v>
       </c>
       <c r="AE42" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF42" s="43" t="inlineStr">
         <is>
@@ -7575,16 +7573,16 @@
         </is>
       </c>
       <c r="AM42" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN42" s="45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="46" t="inlineStr">
         <is>
-          <t>Angela Patricia Barreto Maya</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="B43" s="47" t="inlineStr">
@@ -7594,7 +7592,7 @@
       </c>
       <c r="C43" s="47" t="inlineStr">
         <is>
-          <t>59269721500</t>
+          <t>58803522300</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
@@ -7662,10 +7660,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q43" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="R43" s="49" t="n">
         <v>1</v>
@@ -7694,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="X43" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y43" s="48" t="inlineStr">
         <is>
@@ -7726,10 +7722,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AE43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AE43" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="AF43" s="48" t="inlineStr">
         <is>
@@ -7770,13 +7764,13 @@
         <v>1</v>
       </c>
       <c r="AN43" s="45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>Oscar Acevedo Patiño</t>
+          <t>Angela Patricia Barreto Maya</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -7786,7 +7780,7 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>57197327858</t>
+          <t>59269721500</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -7819,8 +7813,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J44" s="37" t="n">
-        <v>2</v>
+      <c r="J44" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
@@ -7857,10 +7853,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R44" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R44" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="S44" s="39" t="inlineStr">
         <is>
@@ -7882,21 +7876,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W44" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W44" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X44" s="57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z44" s="23" t="n">
-        <v>1</v>
+      <c r="Z44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA44" s="40" t="inlineStr">
         <is>
@@ -7913,11 +7907,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD44" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="42" t="n">
-        <v>3</v>
+      <c r="AD44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE44" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF44" s="43" t="inlineStr">
         <is>
@@ -7958,13 +7956,13 @@
         <v>1</v>
       </c>
       <c r="AN44" s="45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="B45" s="47" t="inlineStr">
@@ -7974,7 +7972,7 @@
       </c>
       <c r="C45" s="47" t="inlineStr">
         <is>
-          <t>7005142049</t>
+          <t>57197327858</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
@@ -8008,7 +8006,7 @@
         </is>
       </c>
       <c r="J45" s="51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" s="48" t="inlineStr">
         <is>
@@ -8040,8 +8038,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q45" s="51" t="n">
-        <v>9</v>
+      <c r="Q45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R45" s="48" t="inlineStr">
         <is>
@@ -8074,15 +8074,15 @@
         </is>
       </c>
       <c r="X45" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="Y45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z45" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="48" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>1</v>
       </c>
       <c r="AE45" s="51" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="48" t="inlineStr">
         <is>
@@ -8135,20 +8135,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL45" s="51" t="n">
-        <v>1</v>
+      <c r="AL45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM45" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN45" s="45" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
@@ -8158,7 +8160,7 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>57205400052</t>
+          <t>7005142049</t>
         </is>
       </c>
       <c r="D46" s="35" t="inlineStr">
@@ -8191,10 +8193,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J46" s="37" t="n">
+        <v>4</v>
       </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="Q46" s="55" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R46" s="39" t="inlineStr">
         <is>
@@ -8260,15 +8260,15 @@
         </is>
       </c>
       <c r="X46" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y46" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z46" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="Y46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA46" s="40" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="AE46" s="42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF46" s="43" t="inlineStr">
         <is>
@@ -8321,22 +8321,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL46" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL46" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM46" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN46" s="45" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="46" t="inlineStr">
         <is>
-          <t>Lien Neil Tejeda López</t>
+          <t>Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -8346,7 +8344,7 @@
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>60026192200</t>
+          <t>57205400052</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
@@ -8414,10 +8412,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q47" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="R47" s="48" t="inlineStr">
         <is>
@@ -8449,23 +8445,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X47" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="Y47" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA47" s="58" t="n">
-        <v>1</v>
+      <c r="Z47" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB47" s="48" t="inlineStr">
         <is>
@@ -8481,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="AE47" s="51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF47" s="48" t="inlineStr">
         <is>
@@ -8522,13 +8516,13 @@
         <v>1</v>
       </c>
       <c r="AN47" s="45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="33" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Lien Neil Tejeda López</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
@@ -8538,7 +8532,7 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>57197028938</t>
+          <t>60026192200</t>
         </is>
       </c>
       <c r="D48" s="35" t="inlineStr">
@@ -8646,18 +8640,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y48" s="22" t="n">
-        <v>1</v>
+      <c r="Y48" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z48" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA48" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA48" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="AB48" s="40" t="inlineStr">
         <is>
@@ -10924,10 +10918,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH61" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI61" s="48" t="inlineStr">
         <is>
@@ -10939,21 +10931,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK61" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL61" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM61" s="44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN61" s="45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -14604,7 +14592,7 @@
         <v>9</v>
       </c>
       <c r="AF82" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG82" s="28" t="n">
         <v>2</v>
@@ -14623,16 +14611,16 @@
         </is>
       </c>
       <c r="AK82" s="45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL82" s="59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -14592,7 +14592,7 @@
         <v>9</v>
       </c>
       <c r="AF82" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG82" s="28" t="n">
         <v>2</v>
@@ -14611,16 +14611,16 @@
         </is>
       </c>
       <c r="AK82" s="45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL82" s="59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -15403,8 +15403,10 @@
       <c r="Y87" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="Z87" s="52" t="n">
-        <v>1</v>
+      <c r="Z87" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA87" s="48" t="inlineStr">
         <is>
@@ -15422,16 +15424,16 @@
         </is>
       </c>
       <c r="AD87" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE87" s="51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF87" s="49" t="n">
         <v>2</v>
       </c>
       <c r="AG87" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH87" s="48" t="inlineStr">
         <is>
@@ -15449,10 +15451,10 @@
         </is>
       </c>
       <c r="AK87" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL87" s="51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM87" s="44" t="n">
         <v>6</v>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -1488,10 +1488,8 @@
       <c r="J7" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="K7" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K7" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="L7" s="52" t="n">
         <v>1</v>
@@ -1518,12 +1516,10 @@
         <v>5</v>
       </c>
       <c r="R7" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="S7" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="T7" s="48" t="inlineStr">
         <is>
@@ -1547,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="Y7" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="48" t="inlineStr">
         <is>
@@ -1576,12 +1572,10 @@
         <v>9</v>
       </c>
       <c r="AF7" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG7" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="AG7" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH7" s="48" t="inlineStr">
         <is>
@@ -1854,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="R9" s="49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S9" s="48" t="inlineStr">
         <is>
@@ -1864,10 +1858,8 @@
       <c r="T9" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U9" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V9" s="48" t="inlineStr">
         <is>
@@ -1913,10 +1905,8 @@
       <c r="AE9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF9" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="AG9" s="48" t="inlineStr">
         <is>
@@ -1928,10 +1918,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI9" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI9" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ9" s="48" t="inlineStr">
         <is>
@@ -2065,7 +2053,7 @@
         <v>4</v>
       </c>
       <c r="Y10" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z10" s="40" t="inlineStr">
         <is>
@@ -2096,10 +2084,8 @@
       <c r="AF10" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="AG10" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG10" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH10" s="43" t="inlineStr">
         <is>
@@ -2557,10 +2543,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N13" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O13" s="48" t="inlineStr">
         <is>
@@ -2708,10 +2692,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H14" s="35" t="inlineStr">
         <is>
@@ -3724,10 +3706,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U19" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U19" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V19" s="48" t="inlineStr">
         <is>
@@ -3757,10 +3737,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB19" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB19" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC19" s="48" t="inlineStr">
         <is>
@@ -3883,10 +3861,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N20" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N20" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O20" s="38" t="inlineStr">
         <is>
@@ -4394,7 +4370,7 @@
         </is>
       </c>
       <c r="D25" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="52" t="n">
         <v>1</v>
@@ -4567,15 +4543,13 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="35" t="inlineStr">
         <is>
@@ -4594,10 +4568,8 @@
       <c r="L26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M26" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
@@ -4616,7 +4588,7 @@
         <v>14</v>
       </c>
       <c r="R26" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S26" s="39" t="inlineStr">
         <is>
@@ -4626,10 +4598,8 @@
       <c r="T26" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="U26" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U26" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V26" s="39" t="inlineStr">
         <is>
@@ -4669,10 +4639,8 @@
       <c r="AE26" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AF26" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF26" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG26" s="43" t="inlineStr">
         <is>
@@ -4843,7 +4811,7 @@
         </is>
       </c>
       <c r="AG27" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH27" s="48" t="inlineStr">
         <is>
@@ -5581,10 +5549,8 @@
           <t>57024211000</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D32" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
@@ -5776,10 +5742,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G33" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H33" s="48" t="inlineStr">
         <is>
@@ -5836,10 +5800,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U33" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="V33" s="48" t="inlineStr">
         <is>
@@ -5867,10 +5829,8 @@
       <c r="AA33" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="AB33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB33" s="53" t="n">
+        <v>3</v>
       </c>
       <c r="AC33" s="48" t="inlineStr">
         <is>
@@ -5898,10 +5858,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI33" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ33" s="48" t="inlineStr">
         <is>
@@ -5940,7 +5898,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
@@ -6059,10 +6017,8 @@
       <c r="AE34" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="AF34" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF34" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG34" s="43" t="inlineStr">
         <is>
@@ -6354,10 +6310,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S36" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S36" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="T36" s="39" t="inlineStr">
         <is>
@@ -6537,10 +6491,8 @@
       <c r="Q37" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="R37" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R37" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S37" s="48" t="inlineStr">
         <is>
@@ -6614,10 +6566,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI37" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI37" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ37" s="48" t="inlineStr">
         <is>
@@ -7490,10 +7440,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U42" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U42" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V42" s="39" t="inlineStr">
         <is>
@@ -7702,10 +7650,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA43" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AB43" s="48" t="inlineStr">
         <is>
@@ -7990,10 +7936,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G45" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H45" s="48" t="inlineStr">
         <is>
@@ -8053,10 +7997,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T45" s="58" t="n">
+        <v>2</v>
       </c>
       <c r="U45" s="48" t="inlineStr">
         <is>
@@ -8084,10 +8026,8 @@
       <c r="Z45" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="AA45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA45" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AB45" s="48" t="inlineStr">
         <is>
@@ -8178,10 +8118,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
@@ -8211,10 +8149,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N46" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N46" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="O46" s="38" t="inlineStr">
         <is>
@@ -8263,7 +8199,7 @@
         <v>5</v>
       </c>
       <c r="Y46" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z46" s="40" t="inlineStr">
         <is>
@@ -8275,10 +8211,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB46" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB46" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="AC46" s="40" t="inlineStr">
         <is>
@@ -8306,10 +8240,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI46" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI46" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ46" s="43" t="inlineStr">
         <is>
@@ -9510,10 +9442,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G53" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="H53" s="48" t="inlineStr">
         <is>
@@ -9648,10 +9578,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI53" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI53" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ53" s="48" t="inlineStr">
         <is>
@@ -10094,10 +10022,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G56" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H56" s="35" t="inlineStr">
         <is>
@@ -10290,10 +10216,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G57" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H57" s="48" t="inlineStr">
         <is>
@@ -10544,7 +10468,7 @@
         <v>2</v>
       </c>
       <c r="U59" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V59" s="48" t="inlineStr">
         <is>
@@ -11973,7 +11897,7 @@
         </is>
       </c>
       <c r="AF67" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG67" s="48" t="inlineStr">
         <is>
@@ -12068,10 +11992,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N68" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N68" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="O68" s="38" t="inlineStr">
         <is>
@@ -12091,10 +12013,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S68" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S68" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="T68" s="19" t="n">
         <v>1</v>
@@ -12771,10 +12691,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H72" s="35" t="inlineStr">
         <is>
@@ -14724,10 +14642,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA83" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA83" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AB83" s="48" t="inlineStr">
         <is>
@@ -14833,10 +14749,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N84" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N84" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O84" s="38" t="inlineStr">
         <is>
@@ -14864,10 +14778,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U84" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U84" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="V84" s="39" t="inlineStr">
         <is>
@@ -14886,7 +14798,7 @@
         <v>1</v>
       </c>
       <c r="Z84" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA84" s="40" t="inlineStr">
         <is>
@@ -14920,10 +14832,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI84" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ84" s="43" t="inlineStr">
         <is>
@@ -15169,10 +15079,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N86" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N86" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O86" s="38" t="inlineStr">
         <is>
@@ -15200,10 +15108,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U86" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U86" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="V86" s="39" t="inlineStr">
         <is>
@@ -15222,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="Z86" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA86" s="40" t="inlineStr">
         <is>
@@ -15256,10 +15162,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI86" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI86" s="30" t="n">
+        <v>3</v>
       </c>
       <c r="AJ86" s="43" t="inlineStr">
         <is>
@@ -15408,15 +15312,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA87" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC87" s="48" t="inlineStr">
         <is>
@@ -15492,10 +15392,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G88" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H88" s="35" t="inlineStr">
         <is>
@@ -16412,10 +16310,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G93" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H93" s="48" t="inlineStr">
         <is>
@@ -16445,10 +16341,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N93" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="O93" s="48" t="inlineStr">
         <is>
@@ -16478,10 +16372,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U93" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="V93" s="48" t="inlineStr">
         <is>
@@ -16511,10 +16403,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB93" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC93" s="48" t="inlineStr">
         <is>
@@ -16534,10 +16424,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG93" s="52" t="n">
+        <v>2</v>
       </c>
       <c r="AH93" s="48" t="inlineStr">
         <is>
@@ -16796,10 +16684,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G95" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G95" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H95" s="48" t="inlineStr">
         <is>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -4647,10 +4647,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH26" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH26" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="AI26" s="43" t="inlineStr">
         <is>
@@ -4668,13 +4666,13 @@
         </is>
       </c>
       <c r="AL26" s="59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM26" s="44" t="n">
         <v>10</v>
       </c>
       <c r="AN26" s="45" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
@@ -10492,7 +10490,7 @@
         </is>
       </c>
       <c r="AA59" s="58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB59" s="48" t="inlineStr">
         <is>
@@ -10505,10 +10503,10 @@
         </is>
       </c>
       <c r="AD59" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE59" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF59" s="48" t="inlineStr">
         <is>
@@ -10538,10 +10536,10 @@
         <v>3</v>
       </c>
       <c r="AM59" s="44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN59" s="45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
@@ -15677,10 +15675,8 @@
       <c r="AE89" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="AF89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF89" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="AG89" s="48" t="inlineStr">
         <is>
@@ -15702,21 +15698,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL89" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK89" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL89" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM89" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN89" s="45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scimago JR 2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CiteScore 2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scimago JR 2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CiteScore 2025" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -10491,50 +10491,48 @@
         </is>
       </c>
       <c r="AA59" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD59" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE59" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="AB59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD59" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE59" s="51" t="n">
+      <c r="AF59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG59" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH59" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK59" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="AF59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG59" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI59" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK59" s="50" t="n">
-        <v>3</v>
-      </c>
       <c r="AL59" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM59" s="44" t="n">
         <v>17</v>
@@ -10842,7 +10840,7 @@
         </is>
       </c>
       <c r="AH61" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI61" s="48" t="inlineStr">
         <is>
@@ -10855,16 +10853,16 @@
         </is>
       </c>
       <c r="AK61" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL61" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM61" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN61" s="45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -11042,7 +11040,7 @@
     <row r="63">
       <c r="A63" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B63" s="47" t="inlineStr">
@@ -11052,7 +11050,7 @@
       </c>
       <c r="C63" s="47" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D63" s="48" t="inlineStr">
@@ -11129,32 +11127,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T63" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" s="53" t="n">
-        <v>1</v>
+      <c r="T63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W63" s="50" t="n">
-        <v>2</v>
+      <c r="W63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X63" s="51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z63" s="52" t="n">
+        <v>2</v>
       </c>
       <c r="AA63" s="48" t="inlineStr">
         <is>
@@ -11171,15 +11173,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD63" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE63" s="51" t="n">
+        <v>5</v>
       </c>
       <c r="AF63" s="49" t="n">
         <v>1</v>
@@ -11189,10 +11187,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH63" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI63" s="48" t="inlineStr">
         <is>
@@ -11205,22 +11201,22 @@
         </is>
       </c>
       <c r="AK63" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL63" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM63" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN63" s="45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>William Arellano Cartagena</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -11230,7 +11226,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>58068069000</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -11238,8 +11234,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="8" t="n">
-        <v>1</v>
+      <c r="E64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
@@ -11256,11 +11254,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="37" t="n">
-        <v>1</v>
+      <c r="I64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
@@ -11301,10 +11303,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T64" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T64" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="20" t="n">
         <v>1</v>
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="W64" s="56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X64" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y64" s="40" t="inlineStr">
         <is>
@@ -11335,24 +11335,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB64" s="25" t="n">
-        <v>1</v>
+      <c r="AB64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD64" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE64" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF64" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG64" s="43" t="inlineStr">
         <is>
@@ -11374,15 +11378,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK64" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL64" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM64" s="44" t="n">
         <v>4</v>
@@ -11394,7 +11394,7 @@
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>William Arellano Cartagena</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>58068069000</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -11412,10 +11412,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E65" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F65" s="48" t="inlineStr">
         <is>
@@ -11432,15 +11430,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I65" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K65" s="48" t="inlineStr">
         <is>
@@ -11486,41 +11480,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U65" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W65" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X65" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z65" s="52" t="n">
-        <v>2</v>
+      <c r="Z65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AB65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB65" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC65" s="48" t="inlineStr">
         <is>
@@ -11528,10 +11518,10 @@
         </is>
       </c>
       <c r="AD65" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF65" s="48" t="inlineStr">
         <is>
@@ -11543,8 +11533,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH65" s="58" t="n">
-        <v>1</v>
+      <c r="AH65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI65" s="48" t="inlineStr">
         <is>
@@ -11556,17 +11548,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL65" s="51" t="n">
-        <v>1</v>
+      <c r="AK65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM65" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN65" s="45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -14509,13 +14505,13 @@
         <v>9</v>
       </c>
       <c r="AF82" s="27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG82" s="28" t="n">
         <v>2</v>
       </c>
       <c r="AH82" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI82" s="43" t="inlineStr">
         <is>
@@ -14528,16 +14524,16 @@
         </is>
       </c>
       <c r="AK82" s="45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL82" s="59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
@@ -15860,10 +15856,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH90" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="AI90" s="43" t="inlineStr">
         <is>
@@ -15875,21 +15869,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK90" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM90" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN90" s="45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -26878,8 +26868,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z59" s="52" t="n">
-        <v>1</v>
+      <c r="Z59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA59" s="58" t="n">
         <v>2</v>
@@ -26895,37 +26887,37 @@
         </is>
       </c>
       <c r="AD59" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE59" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="AE59" s="51" t="n">
+      <c r="AF59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG59" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI59" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK59" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="AF59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG59" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI59" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ59" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK59" s="50" t="n">
-        <v>3</v>
-      </c>
       <c r="AL59" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM59" s="44" t="n">
         <v>17</v>
@@ -27235,7 +27227,7 @@
         </is>
       </c>
       <c r="AH61" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI61" s="48" t="inlineStr">
         <is>
@@ -27248,16 +27240,16 @@
         </is>
       </c>
       <c r="AK61" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL61" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM61" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN61" s="45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -27435,7 +27427,7 @@
     <row r="63">
       <c r="A63" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B63" s="47" t="inlineStr">
@@ -27445,7 +27437,7 @@
       </c>
       <c r="C63" s="47" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D63" s="48" t="inlineStr">
@@ -27528,23 +27520,23 @@
         </is>
       </c>
       <c r="U63" s="53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W63" s="50" t="n">
-        <v>2</v>
+      <c r="W63" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X63" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Y63" s="49" t="n">
+        <v>2</v>
       </c>
       <c r="Z63" s="48" t="inlineStr">
         <is>
@@ -27556,25 +27548,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB63" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC63" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD63" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE63" s="51" t="n">
+        <v>5</v>
       </c>
       <c r="AF63" s="49" t="n">
         <v>1</v>
@@ -27584,10 +27570,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH63" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH63" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI63" s="48" t="inlineStr">
         <is>
@@ -27600,22 +27584,22 @@
         </is>
       </c>
       <c r="AK63" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL63" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM63" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN63" s="45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>William Arellano Cartagena</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -27625,7 +27609,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>58068069000</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -27633,8 +27617,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="8" t="n">
-        <v>1</v>
+      <c r="E64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
@@ -27651,11 +27637,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="37" t="n">
-        <v>1</v>
+      <c r="I64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
@@ -27702,7 +27692,7 @@
         </is>
       </c>
       <c r="U64" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64" s="39" t="inlineStr">
         <is>
@@ -27710,10 +27700,10 @@
         </is>
       </c>
       <c r="W64" s="56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X64" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y64" s="40" t="inlineStr">
         <is>
@@ -27730,24 +27720,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB64" s="25" t="n">
-        <v>1</v>
+      <c r="AB64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD64" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE64" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF64" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG64" s="43" t="inlineStr">
         <is>
@@ -27769,15 +27763,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL64" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK64" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL64" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM64" s="44" t="n">
         <v>4</v>
@@ -27789,7 +27779,7 @@
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>William Arellano Cartagena</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -27799,7 +27789,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>58068069000</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -27807,10 +27797,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E65" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F65" s="48" t="inlineStr">
         <is>
@@ -27827,15 +27815,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I65" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="K65" s="48" t="inlineStr">
         <is>
@@ -27882,23 +27866,23 @@
         </is>
       </c>
       <c r="U65" s="53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W65" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X65" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y65" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Y65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z65" s="48" t="inlineStr">
         <is>
@@ -27919,10 +27903,10 @@
         </is>
       </c>
       <c r="AD65" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF65" s="48" t="inlineStr">
         <is>
@@ -27934,8 +27918,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH65" s="58" t="n">
-        <v>1</v>
+      <c r="AH65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI65" s="48" t="inlineStr">
         <is>
@@ -27947,17 +27933,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL65" s="51" t="n">
-        <v>1</v>
+      <c r="AK65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM65" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN65" s="45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -30870,10 +30860,10 @@
         <v>9</v>
       </c>
       <c r="AF82" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG82" s="28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH82" s="29" t="n">
         <v>1</v>
@@ -30889,16 +30879,16 @@
         </is>
       </c>
       <c r="AK82" s="45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL82" s="59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM82" s="44" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN82" s="45" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
@@ -32194,10 +32184,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG90" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH90" s="43" t="inlineStr">
         <is>
@@ -32214,21 +32202,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL90" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK90" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM90" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN90" s="45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
